--- a/docs/downloads/Barrie.xlsx
+++ b/docs/downloads/Barrie.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D491"/>
+  <dimension ref="A1:D490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9575,17 +9575,17 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Jacetine</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Fry</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>jeff@pickleplex.ca</t>
+          <t>jacetinebayno@gmail.com</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -9597,17 +9597,17 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Jacetine</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Wright</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>jacetinebayno@gmail.com</t>
+          <t>akemail11@icloud.com</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -9619,17 +9619,17 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Lorie</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Desjardins</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>akemail11@icloud.com</t>
+          <t>managerdesjardins2015@gmail.com</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -9641,17 +9641,17 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Lorie</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Desjardins</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>managerdesjardins2015@gmail.com</t>
+          <t>lindarush99@gmail.com</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -9663,17 +9663,17 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Chantelle</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Lawrence</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>lindarush99@gmail.com</t>
+          <t>chantelle.l0812@gmail.com</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -9685,17 +9685,17 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Chantelle</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Lawrence</t>
+          <t>Ambrose</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>chantelle.l0812@gmail.com</t>
+          <t>graham_lisa@hotmail.com</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -9707,17 +9707,17 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Treefrog</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Ambrose</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>graham_lisa@hotmail.com</t>
+          <t>j.vogler@treefrog.ca</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -9729,17 +9729,17 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Treefrog</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>Tidi</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>j.vogler@treefrog.ca</t>
+          <t>stidi@herculesca.ca</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -9751,17 +9751,17 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Tidi</t>
+          <t>Rey</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>stidi@herculesca.ca</t>
+          <t>rmrey1976@hotmail.com</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -9773,17 +9773,17 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Rey</t>
+          <t>Legaspi</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>rmrey1976@hotmail.com</t>
+          <t>nicholas.legaspi@thecanadianbrewhouse.com</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -9795,17 +9795,17 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Michele</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Legaspi</t>
+          <t>Bumbacco</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>nicholas.legaspi@thecanadianbrewhouse.com</t>
+          <t>michelebumbacco@gmail.com</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -9817,17 +9817,17 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Michele</t>
+          <t>Leslie</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Bumbacco</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>michelebumbacco@gmail.com</t>
+          <t>leslie.nguyen@bell.net</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -9839,17 +9839,17 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Leslie</t>
+          <t>Jasmyn</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Farquharson</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>leslie.nguyen@bell.net</t>
+          <t>southeastbarrie.admin@f45training.com</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -9861,17 +9861,17 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Jasmyn</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Farquharson</t>
+          <t>Burnett</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>southeastbarrie.admin@f45training.com</t>
+          <t>tiffany.burnett@live.com</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -9883,17 +9883,17 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>DOMINIQUE</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Burnett</t>
+          <t>NGUYEN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>tiffany.burnett@live.com</t>
+          <t>dominiqueti@hotmail.com</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -9905,42 +9905,20 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>DOMINIQUE</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>NGUYEN</t>
+          <t>Waldie</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>dominiqueti@hotmail.com</t>
+          <t>jwaldie13@gmail.com</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
-        <is>
-          <t>barrie@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>Waldie</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>jwaldie13@gmail.com</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Barrie.xlsx
+++ b/docs/downloads/Barrie.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D490"/>
+  <dimension ref="A1:D491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2921,17 +2921,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Doughty</t>
+          <t>Kuznik</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>kmdx01@gmail.com</t>
+          <t>peterfkuznik@gmail.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2943,17 +2943,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Trudy</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kuznik</t>
+          <t>Argue</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>peterfkuznik@gmail.com</t>
+          <t>trudy.argue@hotmail.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2965,17 +2965,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Trudy</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Argue</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>trudy.argue@hotmail.com</t>
+          <t>steph_carter@live.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2987,17 +2987,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Rania</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Hiram</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>steph_carter@live.com</t>
+          <t>raniahiram@gmail.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3009,17 +3009,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Rania</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Hiram</t>
+          <t>Burns</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>raniahiram@gmail.com</t>
+          <t>michelleburnscoach@gmail.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3031,17 +3031,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Billy</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Burns</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>michelleburnscoach@gmail.com</t>
+          <t>billy.miller01@gmail.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3053,17 +3053,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Billy</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>billy.miller01@gmail.com</t>
+          <t>christopheryoung7861@gmail.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3075,17 +3075,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Beau</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>christopheryoung7861@gmail.com</t>
+          <t>beauscott1@gmail.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3097,17 +3097,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Beau</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Boudreau</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>beauscott1@gmail.com</t>
+          <t>kyle.boudreauqb@gmail.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3119,17 +3119,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Boudreau</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>kyle.boudreauqb@gmail.com</t>
+          <t>tedjarvis54@gmail.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3141,17 +3141,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Nick</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Mantas</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>tedjarvis54@gmail.com</t>
+          <t>mantas@rogers.com</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3163,17 +3163,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>Jo-ann</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mantas</t>
+          <t>Giorshev</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>mantas@rogers.com</t>
+          <t>joanngiorshev@gmail.com</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3185,17 +3185,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Jo-ann</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Giorshev</t>
+          <t>Stpierre</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>joanngiorshev@gmail.com</t>
+          <t>stpierre_m@hotmail.com</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3207,17 +3207,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Stpierre</t>
+          <t>Devenyi</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>stpierre_m@hotmail.com</t>
+          <t>b.devenyi@me.com</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3229,17 +3229,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Rhonda</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Devenyi</t>
+          <t>Bailey</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>b.devenyi@me.com</t>
+          <t>rlbailet60@gmail.com</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3251,17 +3251,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Rhonda</t>
+          <t>Jaskiran</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Nijjar</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>rlbailet60@gmail.com</t>
+          <t>jaskiranamrinder@gmail.com</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3273,17 +3273,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Jaskiran</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nijjar</t>
+          <t>Mcfadyen</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jaskiranamrinder@gmail.com</t>
+          <t>blackstonepba@outlook.com</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3295,17 +3295,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Colin</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mcfadyen</t>
+          <t>Simons</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>blackstonepba@outlook.com</t>
+          <t>integrated@rogers.com</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3317,17 +3317,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Simons</t>
+          <t>Elsharouny</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>integrated@rogers.com</t>
+          <t>sandrasami93@gmail.com</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3339,17 +3339,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Brad</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Elsharouny</t>
+          <t>Brooker</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>sandrasami93@gmail.com</t>
+          <t>brad@bradstreeservice.ca</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3361,17 +3361,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Brad</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Brooker</t>
+          <t>Peckham</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>brad@bradstreeservice.ca</t>
+          <t>carl_niki@sympatico.ca</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3383,17 +3383,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Peckham</t>
+          <t>Beck</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>carl_niki@sympatico.ca</t>
+          <t>mbpei997@gmail.com</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3405,17 +3405,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Suzanna</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Beck</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>mbpei997@gmail.com</t>
+          <t>billyandsuzie16@gmail.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3427,17 +3427,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Suzanna</t>
+          <t>Ralph</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Arends</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>billyandsuzie16@gmail.com</t>
+          <t>ralph@affinityone.ca</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3449,17 +3449,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Ralph</t>
+          <t>Bishoy</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Arends</t>
+          <t>Deif</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ralph@affinityone.ca</t>
+          <t>bishoydeif@gmail.com</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3471,17 +3471,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Bishoy</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deif</t>
+          <t>Carr</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>bishoydeif@gmail.com</t>
+          <t>nancycarr229@gmail.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3493,17 +3493,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Shirlene</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Carr</t>
+          <t>Borczon</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>nancycarr229@gmail.com</t>
+          <t>sborczon@gmail.com</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3515,17 +3515,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Shirlene</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Borczon</t>
+          <t>Waddell</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>sborczon@gmail.com</t>
+          <t>alibredom@gmail.com</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3537,17 +3537,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Beth</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Waddell</t>
+          <t>Collett-reinders</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>alibredom@gmail.com</t>
+          <t>breinders4364@gmail.com</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3559,17 +3559,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Beth</t>
+          <t>Uvisthra</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Collett-reinders</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>breinders4364@gmail.com</t>
+          <t>uvis@ahobf.ca</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3581,17 +3581,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Uvisthra</t>
+          <t>Phyllis</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Rato-hatch</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>uvis@ahobf.ca</t>
+          <t>pratohatch@gmail.com</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3603,17 +3603,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Phyllis</t>
+          <t>Roger</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Rato-hatch</t>
+          <t>Denize</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>pratohatch@gmail.com</t>
+          <t>roger.denize@sympatico.ca</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3625,19 +3625,15 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Roger</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Denize</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>roger.denize@sympatico.ca</t>
-        </is>
-      </c>
+          <t>Nayyar</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -3647,12 +3643,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Nayyar</t>
+          <t>Kotowycz</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3665,12 +3661,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Lewin</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Kotowycz</t>
+          <t>Fakin</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -3683,12 +3679,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Lewin</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Fakin</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3701,12 +3697,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Birch</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3719,12 +3715,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Ayanna</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Birch</t>
+          <t>Ayippey</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3737,12 +3733,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ayanna</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ayippey</t>
+          <t>Driver</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3755,12 +3751,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Marshall</t>
+          <t>Alexia</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Driver</t>
+          <t>Kiathavisack</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -3773,12 +3769,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Alexia</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Kiathavisack</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -3791,12 +3787,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Ellie</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3809,12 +3805,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ellie</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3827,12 +3823,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Ortwein</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -3845,12 +3841,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Sachit</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ortwein</t>
+          <t>Jaat</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -3863,12 +3859,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sachit</t>
+          <t>Leah</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Jaat</t>
+          <t>Vordemberge</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -3881,12 +3877,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Leah</t>
+          <t>Michele</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Vordemberge</t>
+          <t>Mcconney</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -3899,12 +3895,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Michele</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mcconney</t>
+          <t>Beleskey</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -3917,12 +3913,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Silvia</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Beleskey</t>
+          <t>Vilchez</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -3935,12 +3931,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Silvia</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Vilchez</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3953,12 +3949,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>House</t>
+          <t>Crowe</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3971,12 +3967,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Colten</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Crowe</t>
+          <t>Cairncross</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3989,12 +3985,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Colten</t>
+          <t>Claire</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Cairncross</t>
+          <t>Galvez</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -4007,12 +4003,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Claire</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Galvez</t>
+          <t>Kett</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -4025,12 +4021,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Tori</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Kett</t>
+          <t>Sko</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -4043,12 +4039,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Tori</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Sko</t>
+          <t>Szentes</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -4061,12 +4057,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Szentes</t>
+          <t>Mione</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -4079,12 +4075,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mione</t>
+          <t>Mathel</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -4097,12 +4093,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Mathel</t>
+          <t>Bauman</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -4115,12 +4111,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Ellen</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Bauman</t>
+          <t>Marks</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4133,12 +4129,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ellen</t>
+          <t>Levi</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Marks</t>
+          <t>Griffin</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4151,12 +4147,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Levi</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Griffin</t>
+          <t>Montes</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -4169,12 +4165,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Kathleen</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Montes</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -4187,12 +4183,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Kathleen</t>
+          <t>Elwyn</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Deng</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -4205,12 +4201,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Elwyn</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Deng</t>
+          <t>Meerburg</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -4223,12 +4219,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Meerburg</t>
+          <t>D'Aprile</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -4241,12 +4237,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>D'Aprile</t>
+          <t>Deng</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -4259,12 +4255,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Deng</t>
+          <t>Mayers</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -4277,12 +4273,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Mayers</t>
+          <t>Rodrigues</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4295,12 +4291,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Rodrigues</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4313,12 +4309,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Nathalie</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Marquis</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4331,12 +4327,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Nathalie</t>
+          <t>Carson</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Marquis</t>
+          <t>Michaels</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -4349,12 +4345,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Carson</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Michaels</t>
+          <t>Climenhage</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4367,12 +4363,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Shelia</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Climenhage</t>
+          <t>Grosso</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -4385,12 +4381,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Shelia</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Grosso</t>
+          <t>Wickham</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4403,12 +4399,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Wickham</t>
+          <t>Griffin</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4421,7 +4417,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4439,12 +4435,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>Brendan</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Griffin</t>
+          <t>Barrett-Hamilton</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4457,12 +4453,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Brendan</t>
+          <t>Ophelia</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Barrett-Hamilton</t>
+          <t>Berridge Kassam</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -4475,12 +4471,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Ophelia</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Berridge Kassam</t>
+          <t>Champaign</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4493,12 +4489,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>ann-marie</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Champaign</t>
+          <t>Kungal</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4511,12 +4507,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ann-marie</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Kungal</t>
+          <t>Snyder</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -4529,12 +4525,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Snyder</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4547,12 +4543,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Vince</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Valentino</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4565,12 +4561,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Vince</t>
+          <t>Cam</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Valentino</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4583,12 +4579,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Cam</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>S.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -4601,12 +4597,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>S.</t>
+          <t>Saab</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4619,12 +4615,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Saab</t>
+          <t>Kotva</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4637,12 +4633,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Kotva</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4655,12 +4651,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Kotva</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4673,12 +4669,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Vanessa</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Kotva</t>
+          <t>Hurley</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -4691,12 +4687,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Hurley</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -4709,12 +4705,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -4727,12 +4723,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Pete</t>
+          <t>Megan</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Wright</t>
+          <t>Crowe</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -4745,12 +4741,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Crowe</t>
+          <t>Rumney</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -4763,12 +4759,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Rumney</t>
+          <t>Grieve</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -4781,12 +4777,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Dylian</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Grieve</t>
+          <t>Esposito</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -4799,12 +4795,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Dylian</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Esposito</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -4817,12 +4813,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Maverick</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4835,12 +4831,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Maverick</t>
+          <t>Vinod</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4853,12 +4849,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Vinod</t>
+          <t>Brayden</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Laurin</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -4871,12 +4867,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Brayden</t>
+          <t>Anatoly</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Laurin</t>
+          <t>Dobrovinsky</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4889,12 +4885,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Anatoly</t>
+          <t>Anders</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Dobrovinsky</t>
+          <t>Carson</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4907,12 +4903,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Anders</t>
+          <t>Jen</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Carson</t>
+          <t>Simicsak</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4925,12 +4921,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Jen</t>
+          <t>Cathy</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Simicsak</t>
+          <t>Andrews</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4943,12 +4939,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Cathy</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Andrews</t>
+          <t>Snyder</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -4961,12 +4957,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Everett</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Snyder</t>
+          <t>Hotham</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4979,12 +4975,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Everett</t>
+          <t>Corey</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Hotham</t>
+          <t>French</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4997,12 +4993,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Corey</t>
+          <t>Zac</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Mccullough</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -5015,12 +5011,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Zac</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mccullough</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -5033,12 +5029,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Dos Santos</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -5051,12 +5047,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Dos Santos</t>
+          <t>Sier</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -5069,12 +5065,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Sier</t>
+          <t>Tawfik</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -5087,12 +5083,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Tawfik</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -5105,12 +5101,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Tiemersma</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -5128,7 +5124,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Tiemersma</t>
+          <t>Anderton</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -5141,12 +5137,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Anderton</t>
+          <t>Rudkins</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -5159,12 +5155,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Rudkins</t>
+          <t>S.</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -5177,12 +5173,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Kezia</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>S.</t>
+          <t>Holden</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -5195,12 +5191,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Kezia</t>
+          <t>Shaurya</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Holden</t>
+          <t>Sapra</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -5213,12 +5209,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Shaurya</t>
+          <t>Jenn</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Sapra</t>
+          <t>Alberga</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -5231,12 +5227,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Jenn</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Alberga</t>
+          <t>Berry</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -5249,12 +5245,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Helga</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Berry</t>
+          <t>Meerburg</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -5267,12 +5263,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Helga</t>
+          <t>Violet</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Meerburg</t>
+          <t>Hotham</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -5285,12 +5281,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>Don</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Hotham</t>
+          <t>Coulson</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5303,12 +5299,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Don</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Coulson</t>
+          <t>R.</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -5321,12 +5317,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Odin</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>R.</t>
+          <t>Berridge Kassam</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5339,12 +5335,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Odin</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Berridge Kassam</t>
+          <t>Raines</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5357,12 +5353,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Raines</t>
+          <t>Payne</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -5375,12 +5371,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Payne</t>
+          <t>Snyder</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -5393,12 +5389,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Arjan</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Snyder</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5411,12 +5407,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Arjan</t>
+          <t>Xavi</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Kiathavisack</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5429,12 +5425,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Xavi</t>
+          <t>Finn</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Kiathavisack</t>
+          <t>O’Neill</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -5447,12 +5443,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Finn</t>
+          <t>Ella</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>O’Neill</t>
+          <t>Ortwein</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5465,12 +5461,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Ella</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Ortwein</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5483,15 +5479,19 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Jacquie</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>House</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr"/>
+          <t>Balbirnie</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>armellin@outlook.com</t>
+        </is>
+      </c>
       <c r="D249" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -5501,19 +5501,15 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Jacquie</t>
+          <t>Inniyen</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Balbirnie</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>armellin@outlook.com</t>
-        </is>
-      </c>
+          <t>Dhivya Akilan</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -5523,12 +5519,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Inniyen</t>
+          <t>Caiden</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Dhivya Akilan</t>
+          <t>Mumby</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5541,12 +5537,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Caiden</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Mumby</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5559,7 +5555,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5577,12 +5573,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Hoy</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5595,12 +5591,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Hoy</t>
+          <t>Cochrane</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5613,12 +5609,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Jenn</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Cochrane</t>
+          <t>Woyce</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -5631,12 +5627,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Jenn</t>
+          <t>Amaya</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Woyce</t>
+          <t>Doucette</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5649,12 +5645,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Amaya</t>
+          <t>Ignus</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Doucette</t>
+          <t>VanPletsen</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5667,12 +5663,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Ignus</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>VanPletsen</t>
+          <t>Racioppa</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5685,12 +5681,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Gary</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Racioppa</t>
+          <t>Helmkay</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5703,12 +5699,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Gary</t>
+          <t>Aidan</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Helmkay</t>
+          <t>Robertson</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -5721,12 +5717,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Aidan</t>
+          <t>Esai</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Robertson</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -5739,12 +5735,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Esai</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Lorriman</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5757,12 +5753,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Lorriman</t>
+          <t>bergsma</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -5775,12 +5771,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>bergsma</t>
+          <t>Burton</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -5793,12 +5789,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Burton</t>
+          <t>jones</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -5811,12 +5807,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>jones</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5829,12 +5825,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -5847,12 +5843,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Francoeur</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -5865,12 +5861,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Jamie</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Francoeur</t>
+          <t>Bayes</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -5883,12 +5879,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Bayes</t>
+          <t>Woolsey</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -5901,12 +5897,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Colton</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Woolsey</t>
+          <t>Cairncross</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -5919,12 +5915,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Colton</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Cairncross</t>
+          <t>Leblanc</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -5937,12 +5933,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Leblanc</t>
+          <t>Pettifer</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -5955,12 +5951,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Alex JR</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Pettifer</t>
+          <t>Dorbyk</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -5973,12 +5969,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Alex JR</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Dorbyk</t>
+          <t>McCowan</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -5991,12 +5987,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Clare</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>McCowan</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -6009,12 +6005,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Clare</t>
+          <t>Diana</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Kopp</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -6027,12 +6023,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Diana</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Kopp</t>
+          <t>Ramsay</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -6045,12 +6041,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Ramsay</t>
+          <t>Sanderson</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -6063,12 +6059,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Sanderson</t>
+          <t>Reeki</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -6081,12 +6077,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Reeki</t>
+          <t>Sanderson</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -6099,12 +6095,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Trina</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Sanderson</t>
+          <t>Dugay</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -6117,12 +6113,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Trina</t>
+          <t>Arlene</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dugay</t>
+          <t>Kavanangh</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -6135,12 +6131,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Arlene</t>
+          <t>Lesley</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Kavanangh</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -6153,12 +6149,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Lesley</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Wieland</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -6171,12 +6167,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Wieland</t>
+          <t>Kubista</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -6189,12 +6185,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Ronda</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Kubista</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -6207,12 +6203,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ronda</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Abbotts</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -6225,12 +6221,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Caroline</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Abbotts</t>
+          <t>Eden</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -6243,12 +6239,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Caroline</t>
+          <t>jan</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Eden</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -6261,12 +6257,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>jan</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>Slater</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -6279,12 +6275,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Slater</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -6297,12 +6293,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -6315,12 +6311,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -6333,12 +6329,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>brian</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>le</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -6351,12 +6347,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>brian</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>Best</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -6369,12 +6365,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Best</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -6387,12 +6383,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Sarina</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Essner</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -6405,12 +6401,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Sarina</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Essner</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -6423,12 +6419,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Dorothy</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Crump</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -6441,12 +6437,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Dorothy</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Crump</t>
+          <t>Hewitt</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -6459,12 +6455,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Hewitt</t>
+          <t>Gilliland</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -6477,12 +6473,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Ruth</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Gilliland</t>
+          <t>Clubine</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -6495,12 +6491,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Ruth</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Clubine</t>
+          <t>Abbotts</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -6513,12 +6509,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Abbotts</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -6531,12 +6527,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Gord</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Gilroy</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -6549,12 +6545,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Gord</t>
+          <t>Aadarshini</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Gilroy</t>
+          <t>Jeevathas</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -6567,12 +6563,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Aadarshini</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Jeevathas</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -6585,7 +6581,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Juliana</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -6603,12 +6599,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Juliana</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -6621,12 +6617,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
@@ -6639,12 +6635,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Paloma</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -6657,12 +6653,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Rawlings</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -6675,12 +6671,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Rawlings</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -6693,12 +6689,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Pino</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Cellini</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -6711,12 +6707,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Pino</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Cellini</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -6729,12 +6725,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -6747,12 +6743,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Papastathis</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -6765,12 +6761,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Papastathis</t>
+          <t>Talaska</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -6783,12 +6779,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Talaska</t>
+          <t>McFarland</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -6801,12 +6797,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>McFarland</t>
+          <t>Dufort</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -6819,12 +6815,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Dufort</t>
+          <t>Chepurnyj</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -6837,12 +6833,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Chepurnyj</t>
+          <t>Kokelj</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -6855,12 +6851,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Kokelj</t>
+          <t>Reed</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -6873,12 +6869,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>NEHA</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Reed</t>
+          <t>KHARYA</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
@@ -6891,12 +6887,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>NEHA</t>
+          <t>Bailey</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>KHARYA</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -6909,12 +6905,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Levi</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Burt</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
@@ -6927,12 +6923,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Levi</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Burt</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
@@ -6945,12 +6941,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Carly</t>
+          <t>PRISHA</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Dutta</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
@@ -6963,12 +6959,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>PRISHA</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Dutta</t>
+          <t>Macnicol</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
@@ -6981,12 +6977,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>MYRA</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Macnicol</t>
+          <t>Dutta</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
@@ -6999,12 +6995,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>MYRA</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Dutta</t>
+          <t>Kelcey</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
@@ -7017,12 +7013,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Kelcey</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
@@ -7035,12 +7031,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
@@ -7053,12 +7049,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Dagg</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
@@ -7071,12 +7067,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Dagg</t>
+          <t>Correia</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
@@ -7089,12 +7085,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Correia</t>
+          <t>Amato</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
@@ -7107,12 +7103,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Amato</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
@@ -7125,12 +7121,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
@@ -7143,12 +7139,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Meet</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
@@ -7161,12 +7157,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Meet</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Woolsey</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
@@ -7179,12 +7175,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Leeza</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Woolsey</t>
+          <t>Gibbons</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
@@ -7197,12 +7193,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Leeza</t>
+          <t>Chessy</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Gibbons</t>
+          <t>Pottage</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
@@ -7215,12 +7211,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Chessy</t>
+          <t>Maralyn</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Pottage</t>
+          <t>Strachan</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
@@ -7233,12 +7229,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Maralyn</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Strachan</t>
+          <t>Kluszczynski</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
@@ -7251,12 +7247,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Nathiya</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Kluszczynski</t>
+          <t>Sundaralingam</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
@@ -7269,12 +7265,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Nathiya</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Sundaralingam</t>
+          <t>Weller</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
@@ -7287,12 +7283,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Weller</t>
+          <t>Garrod</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
@@ -7305,12 +7301,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Sophie</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Garrod</t>
+          <t>Stonemen</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
@@ -7323,12 +7319,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Sophie</t>
+          <t>Olive</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Stonemen</t>
+          <t>McCowan</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -7341,12 +7337,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>McCowan</t>
+          <t>MacFarlane</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
@@ -7359,12 +7355,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Aj</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>MacFarlane</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
@@ -7377,12 +7373,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Aj</t>
+          <t>Ania</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Nowachzyk</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
@@ -7395,12 +7391,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Ania</t>
+          <t>Rick</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Nowachzyk</t>
+          <t>Lonsdale</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
@@ -7413,12 +7409,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Rick</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Lonsdale</t>
+          <t>Kubista</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
@@ -7431,12 +7427,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Kubista</t>
+          <t>DeCiccio</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
@@ -7449,12 +7445,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>DeCiccio</t>
+          <t>Ferland</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
@@ -7467,12 +7463,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>darcy</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Ferland</t>
+          <t>Woodhall</t>
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
@@ -7485,12 +7481,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>darcy</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Woodhall</t>
+          <t>Hutchison</t>
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
@@ -7503,12 +7499,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Francois</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Hutchison</t>
+          <t>VanPletsen</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
@@ -7521,12 +7517,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Francois</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>VanPletsen</t>
+          <t>Beauchesne</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
@@ -7539,15 +7535,19 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Saima</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Beauchesne</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr"/>
+          <t>Khan</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>saimakhan0803@gmail.com</t>
+        </is>
+      </c>
       <c r="D363" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -7557,17 +7557,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Saima</t>
+          <t>Sally</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t>Keay</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>saimakhan0803@gmail.com</t>
+          <t>smargaretk65@gmail.com</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -7579,17 +7579,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Sally</t>
+          <t>Suzanne</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Keay</t>
+          <t>Dawson</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>smargaretk65@gmail.com</t>
+          <t>smdawson@rogers.com</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -7601,19 +7601,15 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Suzanne</t>
+          <t>Trinex Sports</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Dawson</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>smdawson@rogers.com</t>
-        </is>
-      </c>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -7623,12 +7619,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Trinex Sports</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>Keunen</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
@@ -7641,12 +7637,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Keunen</t>
+          <t>Kotowycz</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
@@ -7659,12 +7655,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Carolina</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Kotowycz</t>
+          <t>Resterpo</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
@@ -7677,12 +7673,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Carolina</t>
+          <t>Shelley</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Resterpo</t>
+          <t>Oran</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
@@ -7695,12 +7691,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Shelley</t>
+          <t>Garry</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Oran</t>
+          <t>Hampton</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
@@ -7713,12 +7709,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Garry</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Hampton</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
@@ -7731,12 +7727,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Janik</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
@@ -7749,12 +7745,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Janik</t>
+          <t>Cosby</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
@@ -7767,12 +7763,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Bhargav</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Cosby</t>
+          <t>Giovani</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
@@ -7785,12 +7781,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Bhargav</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Giovani</t>
+          <t>Keane</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
@@ -7803,12 +7799,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Kyera</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Keane</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
@@ -7821,12 +7817,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Kyera</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
@@ -7839,12 +7835,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
@@ -7857,12 +7853,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
@@ -7875,12 +7871,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Crowe</t>
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
@@ -7893,12 +7889,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Crowe</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
@@ -7911,12 +7907,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Graci</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
@@ -7929,12 +7925,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Graci</t>
+          <t>Guppy</t>
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
@@ -7947,12 +7943,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>glen</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Guppy</t>
+          <t>brophey</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
@@ -7965,12 +7961,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>glen</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>brophey</t>
+          <t>Sin</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
@@ -7983,12 +7979,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Sin</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
@@ -8001,12 +7997,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>Dahlia</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
@@ -8019,12 +8015,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Dahlia</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Evenhuis</t>
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
@@ -8037,12 +8033,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Stephan</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Evenhuis</t>
+          <t>Maier</t>
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
@@ -8055,12 +8051,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Stephan</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Maier</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="C391" t="inlineStr"/>
@@ -8073,12 +8069,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Cameron</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Hoggson</t>
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
@@ -8091,12 +8087,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Cameron</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Hoggson</t>
+          <t>Sauve</t>
         </is>
       </c>
       <c r="C393" t="inlineStr"/>
@@ -8109,12 +8105,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Lesa</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Sauve</t>
+          <t>Doyle</t>
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
@@ -8127,12 +8123,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Lesa</t>
+          <t>Stan</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Doyle</t>
+          <t>Vanderleeuw</t>
         </is>
       </c>
       <c r="C395" t="inlineStr"/>
@@ -8145,12 +8141,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Stan</t>
+          <t>Karissa</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Vanderleeuw</t>
+          <t>Lachance</t>
         </is>
       </c>
       <c r="C396" t="inlineStr"/>
@@ -8163,12 +8159,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Karissa</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Lachance</t>
+          <t>Sangster</t>
         </is>
       </c>
       <c r="C397" t="inlineStr"/>
@@ -8181,12 +8177,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Sangster</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="C398" t="inlineStr"/>
@@ -8199,12 +8195,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>RVH - Team Building</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>RVH</t>
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
@@ -8217,12 +8213,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>RVH - Team Building</t>
+          <t>Hoorang</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>RVH</t>
+          <t>Broujerdi</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -8235,12 +8231,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Hoorang</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Broujerdi</t>
+          <t>Thalheimer</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -8253,12 +8249,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Georgian</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Thalheimer</t>
+          <t>College</t>
         </is>
       </c>
       <c r="C402" t="inlineStr"/>
@@ -8271,12 +8267,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Georgian</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>College</t>
+          <t>Degazio</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -8289,12 +8285,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Degazio</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -8307,12 +8303,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>O'Sullivan</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -8325,12 +8321,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Aj</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>O'Sullivan</t>
+          <t>Carney</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -8343,12 +8339,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Aj</t>
+          <t>RUDRA SINGH</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Carney</t>
+          <t>sangwan</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -8361,12 +8357,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>RUDRA SINGH</t>
+          <t>Destiny</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>sangwan</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
@@ -8379,12 +8375,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Destiny</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Parkin</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
@@ -8397,12 +8393,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Parkin</t>
+          <t>Blom</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
@@ -8415,12 +8411,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Blom</t>
+          <t>Hoare</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
@@ -8433,12 +8429,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Hoare</t>
+          <t>Figliomeni</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
@@ -8451,12 +8447,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Figliomeni</t>
+          <t>Oates</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
@@ -8469,12 +8465,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Oates</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -8487,12 +8483,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Nishank</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -8505,12 +8501,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Nishank</t>
+          <t>Kenny</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -8523,12 +8519,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Kenny</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Walton-Crowe</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -8541,12 +8537,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Walton-Crowe</t>
+          <t>Woolsey</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -8559,12 +8555,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Tori</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Woolsey</t>
+          <t>Maitland</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -8577,12 +8573,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Tori</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Maitland</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -8595,12 +8591,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Rick</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Travers</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -8613,12 +8609,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Rick</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Travers</t>
+          <t>Pham</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -8631,12 +8627,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Elliott</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Pham</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C423" t="inlineStr"/>
@@ -8649,12 +8645,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Elliott</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Ahern</t>
         </is>
       </c>
       <c r="C424" t="inlineStr"/>
@@ -8667,12 +8663,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Tanya</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Ahern</t>
+          <t>van Voorst</t>
         </is>
       </c>
       <c r="C425" t="inlineStr"/>
@@ -8685,12 +8681,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Tanya</t>
+          <t>Landon</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>van Voorst</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="C426" t="inlineStr"/>
@@ -8703,12 +8699,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Landon</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Lougheed</t>
         </is>
       </c>
       <c r="C427" t="inlineStr"/>
@@ -8721,12 +8717,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Lougheed</t>
+          <t>Schubert</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
@@ -8739,12 +8735,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Malia</t>
+          <t>Emmett</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Schubert</t>
+          <t>McLeod</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
@@ -8757,12 +8753,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Emmett</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>McLeod</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
@@ -8775,12 +8771,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Marini</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
@@ -8793,12 +8789,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Marini</t>
+          <t>Basso</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
@@ -8811,12 +8807,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Basso</t>
+          <t>Cristina</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
@@ -8829,12 +8825,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Cristina</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
@@ -8847,12 +8843,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
@@ -8865,12 +8861,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Belo</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
@@ -8883,12 +8879,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Belo</t>
+          <t>Ehman</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
@@ -8901,12 +8897,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Pearce</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Ehman</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="C438" t="inlineStr"/>
@@ -8919,12 +8915,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Pearce</t>
+          <t>Innisfil Cardinals</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>AA Baseball</t>
         </is>
       </c>
       <c r="C439" t="inlineStr"/>
@@ -8937,12 +8933,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Innisfil Cardinals</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>AA Baseball</t>
+          <t>Racioppa</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -8955,12 +8951,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Jilian</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Racioppa</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -8973,12 +8969,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Jilian</t>
+          <t>Rohit</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Iyer</t>
         </is>
       </c>
       <c r="C442" t="inlineStr"/>
@@ -8991,12 +8987,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Rohit</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Iyer</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -9009,12 +9005,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Shiv</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Ratnam</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -9027,12 +9023,12 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Shiv</t>
+          <t>shubham</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Ratnam</t>
+          <t>kataria</t>
         </is>
       </c>
       <c r="C445" t="inlineStr"/>
@@ -9045,12 +9041,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>shubham</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>kataria</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
@@ -9063,12 +9059,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Angus Morrison</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -9081,12 +9077,12 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Angus Morrison</t>
+          <t>Vicky</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Digrado</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -9099,12 +9095,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Vicky</t>
+          <t>Jade</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Digrado</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -9117,12 +9113,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Jade</t>
+          <t>Donald (Ted)</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -9135,12 +9131,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Donald (Ted)</t>
+          <t>Rohit</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Pal</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
@@ -9153,12 +9149,12 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Rohit</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Pal</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
@@ -9171,12 +9167,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Phillips</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -9189,12 +9185,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Phillips</t>
+          <t>Jedrzejewski</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
@@ -9207,12 +9203,12 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Jedrzejewski</t>
+          <t>Knapik</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
@@ -9225,12 +9221,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Jaskiran</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Knapik</t>
+          <t>Nijjar</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -9243,12 +9239,12 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Jaskiran</t>
+          <t>Cassandra</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Nijjar</t>
+          <t>Watson</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
@@ -9261,12 +9257,12 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Cassandra</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Watson</t>
+          <t>Spano</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -9279,12 +9275,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Spano</t>
+          <t>Carre</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -9297,15 +9293,19 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Kaelon</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Carre</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr"/>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>kaelon@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D460" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9315,19 +9315,15 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Kaelon</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Clark</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>kaelon@pickleplexclub.ca</t>
-        </is>
-      </c>
+          <t>Burkitt</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9337,12 +9333,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Burkitt</t>
+          <t>Gardner</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -9355,12 +9351,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Crossfit</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Gardner</t>
+          <t>Pickleball</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -9373,12 +9369,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Crossfit</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Pickleball</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -9391,12 +9387,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>anderson</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -9409,12 +9405,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Suzy</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>anderson</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -9427,7 +9423,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Suzy</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -9445,15 +9441,19 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Ioannou</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr"/>
+          <t>Van rooyen</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>tvanrooyan@rodger.com</t>
+        </is>
+      </c>
       <c r="D468" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9463,19 +9463,15 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>Jasper</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Van rooyen</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>tvanrooyan@rodger.com</t>
-        </is>
-      </c>
+          <t>Varney</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9485,12 +9481,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Jasper</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Varney</t>
+          <t>Tully</t>
         </is>
       </c>
       <c r="C470" t="inlineStr"/>
@@ -9503,12 +9499,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Caleb</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Tully</t>
+          <t>Pena</t>
         </is>
       </c>
       <c r="C471" t="inlineStr"/>
@@ -9521,7 +9517,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Caleb</t>
+          <t>Arnie</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -9539,12 +9535,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Arnie</t>
+          <t>linh</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Pena</t>
+          <t>.</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
@@ -9557,15 +9553,19 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>linh</t>
+          <t>Jacetine</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr"/>
+          <t>Wright</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>jacetinebayno@gmail.com</t>
+        </is>
+      </c>
       <c r="D474" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9575,17 +9575,17 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Jacetine</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Wright</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>jacetinebayno@gmail.com</t>
+          <t>akemail11@icloud.com</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -9597,17 +9597,17 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Lorie</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Desjardins</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>akemail11@icloud.com</t>
+          <t>managerdesjardins2015@gmail.com</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -9619,17 +9619,17 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Lorie</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Desjardins</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>managerdesjardins2015@gmail.com</t>
+          <t>lindarush99@gmail.com</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -9641,17 +9641,17 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Chantelle</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Lawrence</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>lindarush99@gmail.com</t>
+          <t>chantelle.l0812@gmail.com</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -9663,17 +9663,17 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Chantelle</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Lawrence</t>
+          <t>Ambrose</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>chantelle.l0812@gmail.com</t>
+          <t>graham_lisa@hotmail.com</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -9685,17 +9685,17 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Treefrog</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Ambrose</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>graham_lisa@hotmail.com</t>
+          <t>j.vogler@treefrog.ca</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -9707,17 +9707,17 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Treefrog</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>Tidi</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>j.vogler@treefrog.ca</t>
+          <t>stidi@herculesca.ca</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -9729,17 +9729,17 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Tidi</t>
+          <t>Rey</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>stidi@herculesca.ca</t>
+          <t>rmrey1976@hotmail.com</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -9751,17 +9751,17 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Rey</t>
+          <t>Legaspi</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>rmrey1976@hotmail.com</t>
+          <t>nicholas.legaspi@thecanadianbrewhouse.com</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -9773,17 +9773,17 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Michele</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Legaspi</t>
+          <t>Bumbacco</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>nicholas.legaspi@thecanadianbrewhouse.com</t>
+          <t>michelebumbacco@gmail.com</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -9795,17 +9795,17 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Michele</t>
+          <t>Leslie</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Bumbacco</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>michelebumbacco@gmail.com</t>
+          <t>leslie.nguyen@bell.net</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -9817,17 +9817,17 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Leslie</t>
+          <t>Jasmyn</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Farquharson</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>leslie.nguyen@bell.net</t>
+          <t>southeastbarrie.admin@f45training.com</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -9839,17 +9839,17 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Jasmyn</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Farquharson</t>
+          <t>Burnett</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>southeastbarrie.admin@f45training.com</t>
+          <t>tiffany.burnett@live.com</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -9861,17 +9861,17 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Burnett</t>
+          <t>Arpa</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>tiffany.burnett@live.com</t>
+          <t>gillian.arpa@rogers.com</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -9919,6 +9919,28 @@
         </is>
       </c>
       <c r="D490" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Elham</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Emami</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>elham.emami42@gmail.com</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Barrie.xlsx
+++ b/docs/downloads/Barrie.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D538"/>
+  <dimension ref="A1:D562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1689,17 +1689,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Schaschl</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>tony.schaschl@gmail.com</t>
+          <t>nanmohamed11@gmail.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lamarre</t>
+          <t>Schaschl</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jrlamarre@gmail.com</t>
+          <t>tony.schaschl@gmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1733,17 +1733,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Seana</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Frost</t>
+          <t>Lamarre</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>seana.frost16@gmail.com</t>
+          <t>jrlamarre@gmail.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,17 +1755,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Shima</t>
+          <t>Robyn</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Yazdan</t>
+          <t>Percival</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>syazdan52@gmail.com</t>
+          <t>rspercival10@gmail.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Seana</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chalkley</t>
+          <t>Frost</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>peterkeego11@gmail.com</t>
+          <t>seana.frost16@gmail.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Shima</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Galvez</t>
+          <t>Yazdan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>pablo@pablogalvez.com</t>
+          <t>syazdan52@gmail.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Irving</t>
+          <t>Chalkley</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sirving0903@gmail.com</t>
+          <t>peterkeego11@gmail.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mcquigge</t>
+          <t>Galvez</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>mcquiggedoug@gmail.com</t>
+          <t>pablo@pablogalvez.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Morra</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>119csmall@gmail.com</t>
+          <t>chris_morra@outlook.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1887,17 +1887,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Andy</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Mcquigge</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>andypearson550@gmail.com</t>
+          <t>mcquiggedoug@gmail.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1909,17 +1909,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mira</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>mira.ray@gmail.com</t>
+          <t>119csmall@gmail.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cherrie</t>
+          <t>Andy</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mcquigge</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>cherriemcquigge@outlook.com</t>
+          <t>andypearson550@gmail.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Mira</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mcfayden</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>leemcfayden@gmail.com</t>
+          <t>mira.ray@gmail.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1975,17 +1975,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Gin</t>
+          <t>Cherrie</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Facca</t>
+          <t>Mcquigge</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>gina@pickleplecxlub.ca</t>
+          <t>cherriemcquigge@outlook.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1997,17 +1997,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Mcfayden</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>emilymilagreen@outlook.com</t>
+          <t>leemcfayden@gmail.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2019,17 +2019,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ajai</t>
+          <t>Gin</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kudari</t>
+          <t>Facca</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ajaikudari@gmail.com</t>
+          <t>gina@pickleplecxlub.ca</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2041,17 +2041,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Morrison</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>rachel.mike.morrison@gmail.com</t>
+          <t>emilymilagreen@outlook.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2063,17 +2063,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jamie</t>
+          <t>Ajai</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Aitchison</t>
+          <t>Kudari</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jamieaitchison84@gmail.com</t>
+          <t>ajaikudari@gmail.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2085,17 +2085,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Horner</t>
+          <t>Morrison</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kevin.horner@assante.com</t>
+          <t>rachel.mike.morrison@gmail.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2107,17 +2107,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Joanne</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Campagna</t>
+          <t>Aitchison</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>joanneandmike@rogers.com</t>
+          <t>jamieaitchison84@gmail.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2129,17 +2129,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Martina</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wynia</t>
+          <t>Horner</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>martinawynia4@gmail.com</t>
+          <t>kevin.horner@assante.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2151,17 +2151,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ang</t>
+          <t>Joanne</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gontier</t>
+          <t>Campagna</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>originalmoms@gmail.com</t>
+          <t>joanneandmike@rogers.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2173,17 +2173,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Racioppa</t>
+          <t>Wynia</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>maryracioppa27@gmail.com</t>
+          <t>martinawynia4@gmail.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2195,17 +2195,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Peggy</t>
+          <t>Ang</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Milne</t>
+          <t>Gontier</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>peggymilne@mac.com</t>
+          <t>originalmoms@gmail.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Blom</t>
+          <t>Racioppa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>tsblom@gmail.com</t>
+          <t>maryracioppa27@gmail.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2239,17 +2239,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Peggy</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Goedemondt</t>
+          <t>Milne</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>goedemondt@sympatico.ca</t>
+          <t>peggymilne@mac.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2261,17 +2261,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Stacey</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Oostrom</t>
+          <t>Blom</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>staceyoostrom@me.com</t>
+          <t>tsblom@gmail.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2283,17 +2283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Connie</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Graham</t>
+          <t>Goedemondt</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>conniewellsgraham@outlook.com</t>
+          <t>goedemondt@sympatico.ca</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2305,17 +2305,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Steph</t>
+          <t>Stacey</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sier</t>
+          <t>Oostrom</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>stephharrisonx4@gmail.com</t>
+          <t>staceyoostrom@me.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2327,17 +2327,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Rick</t>
+          <t>Connie</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Crane</t>
+          <t>Graham</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>rickdwcrane@gmail.com</t>
+          <t>conniewellsgraham@outlook.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2349,17 +2349,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Somya</t>
+          <t>Steph</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Paliwal</t>
+          <t>Sier</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>somyapaliwal@hotmail.com</t>
+          <t>stephharrisonx4@gmail.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2371,17 +2371,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Carroll</t>
+          <t>Rick</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Balot</t>
+          <t>Crane</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>carroll.balot@utoronto.ca</t>
+          <t>rickdwcrane@gmail.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2393,17 +2393,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Raelene</t>
+          <t>Somya</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Gannon</t>
+          <t>Paliwal</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>raesources@gmail.com</t>
+          <t>somyapaliwal@hotmail.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2415,17 +2415,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Carroll</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Farrugia</t>
+          <t>Balot</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>farrugia2020@yahoo.com</t>
+          <t>carroll.balot@utoronto.ca</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2437,17 +2437,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Yunus</t>
+          <t>Raelene</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Gannon</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>yunusmohamed22@gmail.com</t>
+          <t>raesources@gmail.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2459,17 +2459,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Farrugia</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>craig@aardvark.one</t>
+          <t>farrugia2020@yahoo.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2481,17 +2481,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Yunus</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dick</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sarah_carruthers00@hotmail.com</t>
+          <t>yunusmohamed22@gmail.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2503,17 +2503,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lourenco</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>owenlourenco120@gmail.com</t>
+          <t>craig@aardvark.one</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2525,17 +2525,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Deborah</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Howe</t>
+          <t>Dick</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>debbiehowe2000@yahoo.com</t>
+          <t>sarah_carruthers00@hotmail.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2547,17 +2547,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Grube</t>
+          <t>Lourenco</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>grubee3@gmail.com</t>
+          <t>owenlourenco120@gmail.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2569,17 +2569,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ken</t>
+          <t>Deborah</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Gilmer</t>
+          <t>Howe</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>kenneth.gilmer@garda.com</t>
+          <t>debbiehowe2000@yahoo.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2591,17 +2591,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Kaelon</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Clark</t>
+          <t>Grube</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>kaelonbuckle@outlook.com</t>
+          <t>grubee3@gmail.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2613,17 +2613,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Joanne</t>
+          <t>Ken</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Medeiros</t>
+          <t>Gilmer</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>j95@rogers.com</t>
+          <t>kenneth.gilmer@garda.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2635,17 +2635,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Kaelon</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Amon</t>
+          <t>Clark</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>inch4now@gmail.com</t>
+          <t>kaelonbuckle@outlook.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2657,17 +2657,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Joanne</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Arbour</t>
+          <t>Medeiros</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ames86@live.ca</t>
+          <t>j95@rogers.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2679,17 +2679,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>Amon</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>dcgconsulting@rogers.com</t>
+          <t>inch4now@gmail.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2701,17 +2701,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Holly</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lundrigan</t>
+          <t>Arbour</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>hollster15@hotmail.com</t>
+          <t>ames86@live.ca</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2723,17 +2723,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Hamlin</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>khamlinccimusic@gmail.com</t>
+          <t>dcgconsulting@rogers.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2745,17 +2745,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Holly</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Medeiros</t>
+          <t>Lundrigan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>david@david99.ca</t>
+          <t>hollster15@hotmail.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2767,17 +2767,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Annemarie</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Hill</t>
+          <t>Hamlin</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>lsannemarieh@gmail.com</t>
+          <t>khamlinccimusic@gmail.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2789,17 +2789,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Audree</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Andal</t>
+          <t>Medeiros</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>audree.andal@gmail.com</t>
+          <t>david@david99.ca</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2811,17 +2811,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Brenna</t>
+          <t>Dennis</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Grinnell</t>
+          <t>Miropolsky</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>bkh.mail01@gmail.com</t>
+          <t>dennismirop@gmail.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Janelle</t>
+          <t>Annemarie</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Albert</t>
+          <t>Hill</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>janelle.albert@hotmail.com</t>
+          <t>lsannemarieh@gmail.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2855,17 +2855,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Audree</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Andal</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>codygreen27@hotmail.com</t>
+          <t>audree.andal@gmail.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2877,17 +2877,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Brenna</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nayyar</t>
+          <t>Grinnell</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>samanthanayyar@gmail.ca</t>
+          <t>bkh.mail01@gmail.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2899,17 +2899,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Stan</t>
+          <t>Janelle</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Czachor</t>
+          <t>Albert</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>stanczachor@luxlightingservices.com</t>
+          <t>janelle.albert@hotmail.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2921,17 +2921,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cross</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>mattcross17@hotmail.com</t>
+          <t>codygreen27@hotmail.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2943,17 +2943,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Dannette</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Berard</t>
+          <t>Nayyar</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>carisse1777@gmail.com</t>
+          <t>samanthanayyar@gmail.ca</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2965,17 +2965,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Amrinder</t>
+          <t>Stan</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Kang</t>
+          <t>Czachor</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>280propertymanagement@gmail.com</t>
+          <t>stanczachor@luxlightingservices.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2987,17 +2987,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Colleen</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Crosby</t>
+          <t>Cross</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>cecrosbycct@gmail.com</t>
+          <t>mattcross17@hotmail.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3009,17 +3009,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Dannette</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Blanchard</t>
+          <t>Berard</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ggcc1717@gmail.com</t>
+          <t>carisse1777@gmail.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3031,17 +3031,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kris</t>
+          <t>Amrinder</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Kang</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>kris_johnson11@hotmail.com</t>
+          <t>280propertymanagement@gmail.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3053,17 +3053,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Colleen</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cisneros</t>
+          <t>Crosby</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>manuelcisnerosleyva@gmail.com</t>
+          <t>cecrosbycct@gmail.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3075,17 +3075,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>Blanchard</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>alicia.gauthier@gmail.com</t>
+          <t>ggcc1717@gmail.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3097,17 +3097,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Kris</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Doe</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>cbayford@webersupply.com</t>
+          <t>kris_johnson11@hotmail.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3119,17 +3119,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Desmond</t>
+          <t>Jessie</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Payne</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>dezz.payne@gmail.com</t>
+          <t>yyjessiechan@gmail.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3141,17 +3141,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Beauchesne</t>
+          <t>Cisneros</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>lbeauchesne@smcdsb.on.ca</t>
+          <t>manuelcisnerosleyva@gmail.com</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3163,17 +3163,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kuznik</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>peterfkuznik@gmail.com</t>
+          <t>alicia.gauthier@gmail.com</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3185,17 +3185,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Trudy</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Argue</t>
+          <t>Doe</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>trudy.argue@hotmail.com</t>
+          <t>cbayford@webersupply.com</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3207,17 +3207,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Desmond</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Payne</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>steph_carter@live.com</t>
+          <t>dezz.payne@gmail.com</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3229,17 +3229,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Burns</t>
+          <t>Beauchesne</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>michelleburnscoach@gmail.com</t>
+          <t>lbeauchesne@smcdsb.on.ca</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3251,17 +3251,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Billy</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Kuznik</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>billy.miller01@gmail.com</t>
+          <t>peterfkuznik@gmail.com</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3273,17 +3273,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Trudy</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Argue</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>christopheryoung7861@gmail.com</t>
+          <t>trudy.argue@hotmail.com</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3295,17 +3295,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Beau</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>beauscott1@gmail.com</t>
+          <t>steph_carter@live.com</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3317,17 +3317,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Burns</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>tedjarvis54@gmail.com</t>
+          <t>michelleburnscoach@gmail.com</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3339,17 +3339,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>Billy</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mantas</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>mantas@rogers.com</t>
+          <t>billy.miller01@gmail.com</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3361,17 +3361,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Jo-ann</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Giorshev</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>joanngiorshev@gmail.com</t>
+          <t>christopheryoung7861@gmail.com</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3383,17 +3383,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Beau</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Stpierre</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>stpierre_m@hotmail.com</t>
+          <t>beauscott1@gmail.com</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3405,17 +3405,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Devenyi</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>b.devenyi@me.com</t>
+          <t>tedjarvis54@gmail.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3427,17 +3427,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Rhonda</t>
+          <t>Nick</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Mantas</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>rlbailet60@gmail.com</t>
+          <t>mantas@rogers.com</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3449,17 +3449,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jaskiran</t>
+          <t>Jo-ann</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nijjar</t>
+          <t>Giorshev</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jaskiranamrinder@gmail.com</t>
+          <t>joanngiorshev@gmail.com</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3471,17 +3471,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Colin</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Mcfadyen</t>
+          <t>Stpierre</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>blackstonepba@outlook.com</t>
+          <t>stpierre_m@hotmail.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3493,17 +3493,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Simons</t>
+          <t>Devenyi</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>integrated@rogers.com</t>
+          <t>b.devenyi@me.com</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3515,17 +3515,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Rhonda</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Elsharouny</t>
+          <t>Bailey</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>sandrasami93@gmail.com</t>
+          <t>rlbailet60@gmail.com</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3537,17 +3537,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Brad</t>
+          <t>Jaskiran</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Brooker</t>
+          <t>Nijjar</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>brad@bradstreeservice.ca</t>
+          <t>jaskiranamrinder@gmail.com</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3559,17 +3559,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Fischer</t>
+          <t>Mcfadyen</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>tomf@turfcare.ca</t>
+          <t>blackstonepba@outlook.com</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3581,17 +3581,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Peckham</t>
+          <t>Simons</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>carl_niki@sympatico.ca</t>
+          <t>integrated@rogers.com</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3603,17 +3603,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Beck</t>
+          <t>Elsharouny</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>mbpei997@gmail.com</t>
+          <t>sandrasami93@gmail.com</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3625,17 +3625,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Brad</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Naumovski</t>
+          <t>Brooker</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>rnaumovski@me.com</t>
+          <t>brad@bradstreeservice.ca</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3647,17 +3647,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Suzanna</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Fischer</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>billyandsuzie16@gmail.com</t>
+          <t>tomf@turfcare.ca</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3669,17 +3669,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Ralph</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Arends</t>
+          <t>Peckham</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ralph@affinityone.ca</t>
+          <t>carl_niki@sympatico.ca</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3691,17 +3691,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Bishoy</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Deif</t>
+          <t>Beck</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>bishoydeif@gmail.com</t>
+          <t>mbpei997@gmail.com</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Carr</t>
+          <t>Naumovski</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>nancycarr229@gmail.com</t>
+          <t>rnaumovski@me.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3735,17 +3735,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Shirlene</t>
+          <t>Suzanna</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Borczon</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>sborczon@gmail.com</t>
+          <t>billyandsuzie16@gmail.com</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3757,17 +3757,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Ralph</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Waddell</t>
+          <t>Arends</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>alibredom@gmail.com</t>
+          <t>ralph@affinityone.ca</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3779,17 +3779,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Beth</t>
+          <t>Bishoy</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Collett-reinders</t>
+          <t>Deif</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>breinders4364@gmail.com</t>
+          <t>bishoydeif@gmail.com</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3801,17 +3801,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Uvisthra</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Carr</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>uvis@ahobf.ca</t>
+          <t>nancycarr229@gmail.com</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3823,17 +3823,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Phyllis</t>
+          <t>Shirlene</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Rato-hatch</t>
+          <t>Borczon</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>pratohatch@gmail.com</t>
+          <t>sborczon@gmail.com</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3845,17 +3845,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Carlo</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ciarallo</t>
+          <t>Waddell</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>carlociarallo@hotmail.com</t>
+          <t>alibredom@gmail.com</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3867,17 +3867,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Roger</t>
+          <t>Beth</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Denize</t>
+          <t>Collett-reinders</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>roger.denize@sympatico.ca</t>
+          <t>breinders4364@gmail.com</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3889,15 +3889,19 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Uvisthra</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Nayyar</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>uvis@ahobf.ca</t>
+        </is>
+      </c>
       <c r="D158" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -3907,15 +3911,19 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Phyllis</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Kotowycz</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
+          <t>Rato-hatch</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>pratohatch@gmail.com</t>
+        </is>
+      </c>
       <c r="D159" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -3925,15 +3933,19 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Lewin</t>
+          <t>Carlo</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Fakin</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
+          <t>Ciarallo</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>carlociarallo@hotmail.com</t>
+        </is>
+      </c>
       <c r="D160" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -3943,15 +3955,19 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Roger</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
+          <t>Denize</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>roger.denize@sympatico.ca</t>
+        </is>
+      </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -3961,12 +3977,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Birch</t>
+          <t>Nayyar</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -3979,12 +3995,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ayanna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ayippey</t>
+          <t>Kotowycz</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3997,12 +4013,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Marshall</t>
+          <t>Lewin</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Driver</t>
+          <t>Fakin</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -4015,12 +4031,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Alexia</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Kiathavisack</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -4033,12 +4049,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Birch</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -4051,12 +4067,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ellie</t>
+          <t>Ayanna</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Ayippey</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -4069,12 +4085,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Driver</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -4087,12 +4103,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Alexia</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ortwein</t>
+          <t>Kiathavisack</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -4105,12 +4121,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sachit</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Jaat</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -4123,12 +4139,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Leah</t>
+          <t>Ellie</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Vordemberge</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -4141,12 +4157,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Michele</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Mcconney</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -4159,12 +4175,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Beleskey</t>
+          <t>Ortwein</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4177,12 +4193,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Silvia</t>
+          <t>Sachit</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Vilchez</t>
+          <t>Jaat</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4195,12 +4211,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Leah</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>House</t>
+          <t>Vordemberge</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -4213,12 +4229,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Michele</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Crowe</t>
+          <t>Mcconney</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -4231,12 +4247,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Colten</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Cairncross</t>
+          <t>Beleskey</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -4249,12 +4265,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Claire</t>
+          <t>Silvia</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Galvez</t>
+          <t>Vilchez</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -4267,12 +4283,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Kett</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -4285,12 +4301,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Tori</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Sko</t>
+          <t>Crowe</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -4303,12 +4319,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Colten</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Szentes</t>
+          <t>Cairncross</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -4321,12 +4337,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Claire</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Mione</t>
+          <t>Galvez</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4339,12 +4355,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mathel</t>
+          <t>Kett</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4357,12 +4373,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Tori</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Bauman</t>
+          <t>Sko</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4375,12 +4391,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Ellen</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Marks</t>
+          <t>Szentes</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -4393,12 +4409,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Levi</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Griffin</t>
+          <t>Mione</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4411,12 +4427,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Montes</t>
+          <t>Mathel</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -4429,12 +4445,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Kathleen</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Bauman</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4447,12 +4463,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Elwyn</t>
+          <t>Ellen</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Deng</t>
+          <t>Marks</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4465,12 +4481,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Levi</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Meerburg</t>
+          <t>Griffin</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4483,12 +4499,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>D'Aprile</t>
+          <t>Montes</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4501,12 +4517,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Kathleen</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Deng</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -4519,12 +4535,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Elwyn</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Mayers</t>
+          <t>Deng</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4537,12 +4553,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Rodrigues</t>
+          <t>Meerburg</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4555,12 +4571,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>D'Aprile</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -4573,12 +4589,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Nathalie</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Marquis</t>
+          <t>Deng</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4591,12 +4607,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Carson</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Michaels</t>
+          <t>Mayers</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4609,12 +4625,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Climenhage</t>
+          <t>Rodrigues</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4627,12 +4643,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Shelia</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Grosso</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -4645,12 +4661,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Nathalie</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Wickham</t>
+          <t>Marquis</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4663,12 +4679,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Carson</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Griffin</t>
+          <t>Michaels</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4681,12 +4697,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Griffin</t>
+          <t>Climenhage</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4699,12 +4715,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Brendan</t>
+          <t>Shelia</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Barrett-Hamilton</t>
+          <t>Grosso</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4717,12 +4733,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Ophelia</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Berridge Kassam</t>
+          <t>Wickham</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -4735,12 +4751,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Champaign</t>
+          <t>Griffin</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -4753,12 +4769,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ann-marie</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Kungal</t>
+          <t>Griffin</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -4771,12 +4787,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Brendan</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Snyder</t>
+          <t>Barrett-Hamilton</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -4789,12 +4805,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Ophelia</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Berridge Kassam</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -4807,12 +4823,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Vince</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Valentino</t>
+          <t>Champaign</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -4825,12 +4841,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Cam</t>
+          <t>ann-marie</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Kungal</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -4843,12 +4859,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>S.</t>
+          <t>Snyder</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -4861,12 +4877,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Saab</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4879,12 +4895,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Vince</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Kotva</t>
+          <t>Valentino</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4897,12 +4913,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Cam</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -4915,12 +4931,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Kotva</t>
+          <t>S.</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4933,12 +4949,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Hurley</t>
+          <t>Saab</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4951,12 +4967,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Kotva</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4969,12 +4985,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Pete</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Wright</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4987,12 +5003,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Crowe</t>
+          <t>Kotva</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -5005,12 +5021,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Vanessa</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Rumney</t>
+          <t>Hurley</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -5023,12 +5039,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Grieve</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -5041,12 +5057,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Dylian</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Esposito</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -5059,12 +5075,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Megan</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Crowe</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -5077,12 +5093,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Maverick</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Rumney</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -5095,12 +5111,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Vinod</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Grieve</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -5113,12 +5129,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Brayden</t>
+          <t>Dylian</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Laurin</t>
+          <t>Esposito</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -5131,12 +5147,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Anatoly</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Dobrovinsky</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -5149,12 +5165,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Anders</t>
+          <t>Maverick</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Carson</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -5167,12 +5183,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Jen</t>
+          <t>Vinod</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Simicsak</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -5185,12 +5201,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Cathy</t>
+          <t>Brayden</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Andrews</t>
+          <t>Laurin</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -5203,12 +5219,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Anatoly</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Snyder</t>
+          <t>Dobrovinsky</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -5221,12 +5237,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Everett</t>
+          <t>Anders</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Hotham</t>
+          <t>Carson</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -5239,12 +5255,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Corey</t>
+          <t>Jen</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Simicsak</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -5257,12 +5273,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Zac</t>
+          <t>Cathy</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Mccullough</t>
+          <t>Andrews</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -5275,12 +5291,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Snyder</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -5293,12 +5309,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Everett</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Dos Santos</t>
+          <t>Hotham</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -5311,12 +5327,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Corey</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Sier</t>
+          <t>French</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -5329,12 +5345,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Zac</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Tawfik</t>
+          <t>Mccullough</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5347,7 +5363,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5365,12 +5381,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Tiemersma</t>
+          <t>Dos Santos</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5383,12 +5399,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Anderton</t>
+          <t>Sier</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5401,12 +5417,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Rudkins</t>
+          <t>Tawfik</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -5419,12 +5435,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>S.</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -5437,12 +5453,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Kezia</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Holden</t>
+          <t>Tiemersma</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5455,12 +5471,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Shaurya</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Sapra</t>
+          <t>Anderton</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5473,12 +5489,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Jenn</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Alberga</t>
+          <t>Rudkins</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -5491,12 +5507,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Berry</t>
+          <t>S.</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5509,12 +5525,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Helga</t>
+          <t>Kezia</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Meerburg</t>
+          <t>Holden</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5527,12 +5543,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>Shaurya</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Hotham</t>
+          <t>Sapra</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -5545,12 +5561,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Don</t>
+          <t>Jenn</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Coulson</t>
+          <t>Alberga</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5563,12 +5579,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>R.</t>
+          <t>Berry</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5581,12 +5597,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Odin</t>
+          <t>Helga</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Berridge Kassam</t>
+          <t>Meerburg</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5599,12 +5615,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Violet</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Raines</t>
+          <t>Hotham</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5617,12 +5633,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Don</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Payne</t>
+          <t>Coulson</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5635,12 +5651,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Snyder</t>
+          <t>R.</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5653,12 +5669,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Arjan</t>
+          <t>Odin</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Berridge Kassam</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -5671,12 +5687,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Xavi</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Kiathavisack</t>
+          <t>Raines</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5689,12 +5705,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Finn</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>O’Neill</t>
+          <t>Payne</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5707,12 +5723,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Ella</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Ortwein</t>
+          <t>Snyder</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5725,12 +5741,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Arjan</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>House</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5743,19 +5759,15 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Xavi</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Ang</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>anneang@me.com</t>
-        </is>
-      </c>
+          <t>Kiathavisack</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -5765,19 +5777,15 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Jacquie</t>
+          <t>Finn</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Balbirnie</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>armellin@outlook.com</t>
-        </is>
-      </c>
+          <t>O’Neill</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -5787,12 +5795,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Inniyen</t>
+          <t>Ella</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Dhivya Akilan</t>
+          <t>Ortwein</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5805,12 +5813,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Caiden</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Mumby</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -5823,15 +5831,19 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Jacquie</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Bergen</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr"/>
+          <t>Balbirnie</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>armellin@outlook.com</t>
+        </is>
+      </c>
       <c r="D265" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -5841,12 +5853,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Inniyen</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Dhivya Akilan</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -5859,12 +5871,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Caiden</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Hoy</t>
+          <t>Mumby</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5877,12 +5889,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Cochrane</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -5895,12 +5907,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Jenn</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Woyce</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -5913,12 +5925,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Amaya</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Doucette</t>
+          <t>Hoy</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -5931,12 +5943,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Ignus</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>VanPletsen</t>
+          <t>Cochrane</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -5949,12 +5961,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Jenn</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Racioppa</t>
+          <t>Woyce</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -5967,12 +5979,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Gary</t>
+          <t>Amaya</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Helmkay</t>
+          <t>Doucette</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -5985,12 +5997,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Aidan</t>
+          <t>Ignus</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Robertson</t>
+          <t>VanPletsen</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -6003,12 +6015,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Esai</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Racioppa</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -6021,12 +6033,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Gary</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Lorriman</t>
+          <t>Helmkay</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -6039,12 +6051,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Aidan</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>bergsma</t>
+          <t>Robertson</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -6057,12 +6069,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Esai</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Burton</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -6075,12 +6087,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>jones</t>
+          <t>Lorriman</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -6093,12 +6105,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>bergsma</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -6111,12 +6123,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Burton</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -6129,12 +6141,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Jamie</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Francoeur</t>
+          <t>jones</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -6147,12 +6159,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Bayes</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -6165,12 +6177,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Woolsey</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -6183,12 +6195,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Colton</t>
+          <t>Jamie</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Cairncross</t>
+          <t>Francoeur</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -6201,12 +6213,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Leblanc</t>
+          <t>Bayes</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -6219,12 +6231,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Pettifer</t>
+          <t>Woolsey</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -6237,12 +6249,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Alex JR</t>
+          <t>Colton</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Dorbyk</t>
+          <t>Cairncross</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -6255,12 +6267,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>McCowan</t>
+          <t>Leblanc</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -6273,12 +6285,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Clare</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Pettifer</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -6291,12 +6303,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Diana</t>
+          <t>Alex JR</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Kopp</t>
+          <t>Dorbyk</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -6309,12 +6321,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Ramsay</t>
+          <t>McCowan</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -6327,12 +6339,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Clare</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Sanderson</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -6345,12 +6357,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Diana</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Reeki</t>
+          <t>Kopp</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -6363,12 +6375,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Sanderson</t>
+          <t>Ramsay</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -6381,12 +6393,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Trina</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Dugay</t>
+          <t>Sanderson</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -6399,12 +6411,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Arlene</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Kavanangh</t>
+          <t>Reeki</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -6417,12 +6429,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Lesley</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Sanderson</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -6435,12 +6447,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Trina</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Wieland</t>
+          <t>Dugay</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -6453,12 +6465,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Arlene</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Kubista</t>
+          <t>Kavanangh</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -6471,12 +6483,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Ronda</t>
+          <t>Lesley</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -6489,12 +6501,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Abbotts</t>
+          <t>Wieland</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -6507,12 +6519,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Caroline</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Eden</t>
+          <t>Kubista</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -6525,12 +6537,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>jan</t>
+          <t>Ronda</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -6543,12 +6555,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Slater</t>
+          <t>Abbotts</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -6561,12 +6573,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>Caroline</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Eden</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -6579,12 +6591,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>jan</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -6597,12 +6609,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Slater</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -6615,12 +6627,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>brian</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -6633,12 +6645,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Best</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -6651,12 +6663,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -6669,12 +6681,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Sarina</t>
+          <t>brian</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Essner</t>
+          <t>le</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
@@ -6687,12 +6699,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Best</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -6705,12 +6717,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Dorothy</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Crump</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -6723,12 +6735,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Sarina</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Hewitt</t>
+          <t>Essner</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -6741,12 +6753,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Gilliland</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -6759,12 +6771,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Ruth</t>
+          <t>Dorothy</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Clubine</t>
+          <t>Crump</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -6777,12 +6789,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Abbotts</t>
+          <t>Hewitt</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -6795,12 +6807,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Gilliland</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -6813,12 +6825,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Gord</t>
+          <t>Ruth</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Gilroy</t>
+          <t>Clubine</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -6831,12 +6843,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Aadarshini</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Jeevathas</t>
+          <t>Abbotts</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -6849,12 +6861,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -6867,12 +6879,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Juliana</t>
+          <t>Gord</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Gilroy</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -6885,12 +6897,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Aadarshini</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Jeevathas</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -6903,12 +6915,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Paloma</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -6921,12 +6933,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Juliana</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
@@ -6944,7 +6956,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Rawlings</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -6957,12 +6969,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
@@ -6975,12 +6987,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Pino</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Cellini</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
@@ -6993,12 +7005,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Rawlings</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
@@ -7011,12 +7023,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
@@ -7029,12 +7041,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Pino</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Papastathis</t>
+          <t>Cellini</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
@@ -7047,12 +7059,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Talaska</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
@@ -7065,12 +7077,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>McFarland</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
@@ -7083,12 +7095,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Dufort</t>
+          <t>Papastathis</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
@@ -7101,12 +7113,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Chepurnyj</t>
+          <t>Talaska</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
@@ -7119,12 +7131,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Kokelj</t>
+          <t>McFarland</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
@@ -7137,12 +7149,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Reed</t>
+          <t>Dufort</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
@@ -7155,12 +7167,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>NEHA</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>KHARYA</t>
+          <t>Chepurnyj</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
@@ -7173,12 +7185,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Kokelj</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
@@ -7191,12 +7203,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Levi</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Burt</t>
+          <t>Reed</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
@@ -7209,12 +7221,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Carly</t>
+          <t>NEHA</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>KHARYA</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
@@ -7227,12 +7239,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>PRISHA</t>
+          <t>Bailey</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Dutta</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
@@ -7245,12 +7257,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Levi</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Macnicol</t>
+          <t>Burt</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
@@ -7263,12 +7275,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>MYRA</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Dutta</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
@@ -7281,12 +7293,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>PRISHA</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Kelcey</t>
+          <t>Dutta</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
@@ -7299,12 +7311,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Macnicol</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
@@ -7317,12 +7329,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>MYRA</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Dutta</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
@@ -7335,12 +7347,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Dagg</t>
+          <t>Kelcey</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
@@ -7353,12 +7365,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Correia</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
@@ -7371,12 +7383,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Amato</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -7389,12 +7401,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Dagg</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
@@ -7407,12 +7419,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Correia</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
@@ -7425,12 +7437,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Meet</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Amato</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
@@ -7443,12 +7455,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Woolsey</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
@@ -7461,12 +7473,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Leeza</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Gibbons</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
@@ -7479,12 +7491,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Chessy</t>
+          <t>Meet</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Pottage</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
@@ -7497,12 +7509,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Maralyn</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Strachan</t>
+          <t>Woolsey</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
@@ -7515,12 +7527,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Leeza</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Kluszczynski</t>
+          <t>Gibbons</t>
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
@@ -7533,12 +7545,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Nathiya</t>
+          <t>Chessy</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Sundaralingam</t>
+          <t>Pottage</t>
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
@@ -7551,12 +7563,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Maralyn</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Weller</t>
+          <t>Strachan</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
@@ -7569,12 +7581,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Garrod</t>
+          <t>Kluszczynski</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
@@ -7587,12 +7599,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Sophie</t>
+          <t>Nathiya</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Stonemen</t>
+          <t>Sundaralingam</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
@@ -7605,12 +7617,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>McCowan</t>
+          <t>Weller</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
@@ -7623,12 +7635,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MacFarlane</t>
+          <t>Garrod</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
@@ -7641,12 +7653,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Aj</t>
+          <t>Sophie</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Stonemen</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
@@ -7659,12 +7671,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Ania</t>
+          <t>Olive</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Nowachzyk</t>
+          <t>McCowan</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
@@ -7677,12 +7689,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Rick</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Lonsdale</t>
+          <t>MacFarlane</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
@@ -7695,12 +7707,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Aj</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Kubista</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
@@ -7713,12 +7725,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Ania</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>DeCiccio</t>
+          <t>Nowachzyk</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
@@ -7731,12 +7743,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Rick</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Ferland</t>
+          <t>Lonsdale</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
@@ -7749,12 +7761,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>darcy</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Woodhall</t>
+          <t>Kubista</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
@@ -7767,12 +7779,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Hutchison</t>
+          <t>DeCiccio</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
@@ -7785,12 +7797,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Francois</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>VanPletsen</t>
+          <t>Ferland</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
@@ -7803,12 +7815,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>darcy</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Beauchesne</t>
+          <t>Woodhall</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
@@ -7821,19 +7833,15 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Saima</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Khan</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>saimakhan0803@gmail.com</t>
-        </is>
-      </c>
+          <t>Hutchison</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -7843,19 +7851,15 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Sally</t>
+          <t>Francois</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Keay</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>smargaretk65@gmail.com</t>
-        </is>
-      </c>
+          <t>VanPletsen</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -7865,19 +7869,15 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Suzanne</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Dawson</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>smdawson@rogers.com</t>
-        </is>
-      </c>
+          <t>Beauchesne</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -7887,17 +7887,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Mekayla</t>
+          <t>Saima</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Armellin</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>mekaylaarmellin@gmail.com</t>
+          <t>saimakhan0803@gmail.com</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -7909,15 +7909,19 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Trinex Sports</t>
+          <t>Sally</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr"/>
+          <t>Keay</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>smargaretk65@gmail.com</t>
+        </is>
+      </c>
       <c r="D380" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -7927,15 +7931,19 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Suzanne</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Keunen</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr"/>
+          <t>Dawson</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>smdawson@rogers.com</t>
+        </is>
+      </c>
       <c r="D381" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -7945,15 +7953,19 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Mekayla</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Kotowycz</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr"/>
+          <t>Armellin</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>mekaylaarmellin@gmail.com</t>
+        </is>
+      </c>
       <c r="D382" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -7963,12 +7975,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Carolina</t>
+          <t>Trinex Sports</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Resterpo</t>
+          <t>s</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
@@ -7981,15 +7993,19 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Shelley</t>
+          <t>Ivonne</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Oran</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr"/>
+          <t>Morra</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>ivonne.morra05@gmail.com</t>
+        </is>
+      </c>
       <c r="D384" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -7999,12 +8015,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Garry</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Hampton</t>
+          <t>Keunen</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
@@ -8017,12 +8033,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Kotowycz</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
@@ -8035,12 +8051,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Carolina</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Janik</t>
+          <t>Resterpo</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
@@ -8053,12 +8069,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Shelley</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Cosby</t>
+          <t>Oran</t>
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
@@ -8071,12 +8087,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Bhargav</t>
+          <t>Garry</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Giovani</t>
+          <t>Hampton</t>
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
@@ -8089,12 +8105,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Keane</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
@@ -8107,12 +8123,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Kyera</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Janik</t>
         </is>
       </c>
       <c r="C391" t="inlineStr"/>
@@ -8125,12 +8141,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Cosby</t>
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
@@ -8143,12 +8159,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Bhargav</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Giovani</t>
         </is>
       </c>
       <c r="C393" t="inlineStr"/>
@@ -8161,12 +8177,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Keane</t>
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
@@ -8179,12 +8195,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Kyera</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Crowe</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C395" t="inlineStr"/>
@@ -8197,7 +8213,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -8215,12 +8231,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Graci</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C397" t="inlineStr"/>
@@ -8233,12 +8249,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Guppy</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C398" t="inlineStr"/>
@@ -8251,12 +8267,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>glen</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>brophey</t>
+          <t>Crowe</t>
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
@@ -8269,12 +8285,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Sin</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -8287,12 +8303,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Graci</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -8305,12 +8321,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Dahlia</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Guppy</t>
         </is>
       </c>
       <c r="C402" t="inlineStr"/>
@@ -8323,12 +8339,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>glen</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Evenhuis</t>
+          <t>brophey</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -8341,12 +8357,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Stephan</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Maier</t>
+          <t>Sin</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -8359,12 +8375,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -8377,12 +8393,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Cameron</t>
+          <t>Dahlia</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Hoggson</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -8395,12 +8411,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Sauve</t>
+          <t>Evenhuis</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -8413,12 +8429,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Lesa</t>
+          <t>Stephan</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Doyle</t>
+          <t>Maier</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
@@ -8431,12 +8447,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Stan</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Vanderleeuw</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
@@ -8449,12 +8465,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Karissa</t>
+          <t>Cameron</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Lachance</t>
+          <t>Hoggson</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
@@ -8467,12 +8483,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Sangster</t>
+          <t>Sauve</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
@@ -8485,12 +8501,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Lesa</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Doyle</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
@@ -8503,12 +8519,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>RVH - Team Building</t>
+          <t>Stan</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>RVH</t>
+          <t>Vanderleeuw</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
@@ -8521,12 +8537,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Hoorang</t>
+          <t>Karissa</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Broujerdi</t>
+          <t>Lachance</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -8539,12 +8555,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Thalheimer</t>
+          <t>Sangster</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -8557,12 +8573,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Georgian</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>College</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -8575,12 +8591,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>RVH - Team Building</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Degazio</t>
+          <t>RVH</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -8593,12 +8609,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Hoorang</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Broujerdi</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -8611,12 +8627,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>O'Sullivan</t>
+          <t>Thalheimer</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -8629,12 +8645,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Aj</t>
+          <t>Georgian</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Carney</t>
+          <t>College</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -8647,12 +8663,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>RUDRA SINGH</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>sangwan</t>
+          <t>Degazio</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -8665,12 +8681,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Destiny</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -8688,7 +8704,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Parkin</t>
+          <t>O'Sullivan</t>
         </is>
       </c>
       <c r="C423" t="inlineStr"/>
@@ -8701,12 +8717,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Aj</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Blom</t>
+          <t>Carney</t>
         </is>
       </c>
       <c r="C424" t="inlineStr"/>
@@ -8719,12 +8735,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>RUDRA SINGH</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Hoare</t>
+          <t>sangwan</t>
         </is>
       </c>
       <c r="C425" t="inlineStr"/>
@@ -8737,12 +8753,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Destiny</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Figliomeni</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C426" t="inlineStr"/>
@@ -8755,12 +8771,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Oates</t>
+          <t>Parkin</t>
         </is>
       </c>
       <c r="C427" t="inlineStr"/>
@@ -8773,12 +8789,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Blom</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
@@ -8791,12 +8807,12 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Nishank</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Hoare</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
@@ -8809,12 +8825,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Kenny</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Figliomeni</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
@@ -8827,12 +8843,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Walton-Crowe</t>
+          <t>Oates</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
@@ -8845,12 +8861,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Woolsey</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
@@ -8863,12 +8879,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Tori</t>
+          <t>Nishank</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Maitland</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
@@ -8881,12 +8897,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Kenny</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
@@ -8899,12 +8915,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Rick</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Travers</t>
+          <t>Walton-Crowe</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
@@ -8917,12 +8933,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Pham</t>
+          <t>Woolsey</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
@@ -8935,12 +8951,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Elliott</t>
+          <t>Tori</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Maitland</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
@@ -8953,12 +8969,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Ahern</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="C438" t="inlineStr"/>
@@ -8971,12 +8987,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Tanya</t>
+          <t>Rick</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>van Voorst</t>
+          <t>Travers</t>
         </is>
       </c>
       <c r="C439" t="inlineStr"/>
@@ -8989,12 +9005,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Landon</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Pham</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -9007,12 +9023,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Elliott</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Lougheed</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -9025,12 +9041,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Malia</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Schubert</t>
+          <t>Ahern</t>
         </is>
       </c>
       <c r="C442" t="inlineStr"/>
@@ -9043,12 +9059,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Emmett</t>
+          <t>Tanya</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>McLeod</t>
+          <t>van Voorst</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -9061,12 +9077,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Landon</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -9079,12 +9095,12 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Marini</t>
+          <t>Lougheed</t>
         </is>
       </c>
       <c r="C445" t="inlineStr"/>
@@ -9097,12 +9113,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Basso</t>
+          <t>Schubert</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
@@ -9115,12 +9131,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Emmett</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Cristina</t>
+          <t>McLeod</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -9133,12 +9149,12 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -9151,12 +9167,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Marini</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -9169,12 +9185,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Belo</t>
+          <t>Basso</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -9187,12 +9203,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Ehman</t>
+          <t>Cristina</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
@@ -9205,12 +9221,12 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Pearce</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
@@ -9223,12 +9239,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Innisfil Cardinals</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>AA Baseball</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -9241,12 +9257,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Racioppa</t>
+          <t>Belo</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
@@ -9259,12 +9275,12 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Jilian</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Ehman</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
@@ -9277,12 +9293,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Rohit</t>
+          <t>Pearce</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Iyer</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -9295,12 +9311,12 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Innisfil Cardinals</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>AA Baseball</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
@@ -9313,12 +9329,12 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Shiv</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Ratnam</t>
+          <t>Racioppa</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -9331,12 +9347,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>shubham</t>
+          <t>Jilian</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>kataria</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -9349,12 +9365,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Rohit</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Iyer</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -9367,12 +9383,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Angus Morrison</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -9385,12 +9401,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Vicky</t>
+          <t>Shiv</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Digrado</t>
+          <t>Ratnam</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -9403,12 +9419,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Jade</t>
+          <t>shubham</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Booth</t>
+          <t>kataria</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -9421,12 +9437,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Donald (Ted)</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -9439,12 +9455,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Rohit</t>
+          <t>Angus Morrison</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Pal</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -9457,12 +9473,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Vicky</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Digrado</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -9475,12 +9491,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Jade</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Phillips</t>
+          <t>Booth</t>
         </is>
       </c>
       <c r="C467" t="inlineStr"/>
@@ -9493,12 +9509,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Donald (Ted)</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Jedrzejewski</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="C468" t="inlineStr"/>
@@ -9511,12 +9527,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Rohit</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Knapik</t>
+          <t>Pal</t>
         </is>
       </c>
       <c r="C469" t="inlineStr"/>
@@ -9529,12 +9545,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Jaskiran</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Nijjar</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C470" t="inlineStr"/>
@@ -9547,12 +9563,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Cassandra</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Watson</t>
+          <t>Phillips</t>
         </is>
       </c>
       <c r="C471" t="inlineStr"/>
@@ -9565,12 +9581,12 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Spano</t>
+          <t>Jedrzejewski</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
@@ -9583,12 +9599,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Carre</t>
+          <t>Knapik</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
@@ -9601,19 +9617,15 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Kaelon</t>
+          <t>Jaskiran</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Clark</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>kaelon@pickleplexclub.ca</t>
-        </is>
-      </c>
+          <t>Nijjar</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9623,12 +9635,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Cassandra</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Burkitt</t>
+          <t>Watson</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -9641,12 +9653,12 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Gardner</t>
+          <t>Spano</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
@@ -9659,12 +9671,12 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Crossfit</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Pickleball</t>
+          <t>Carre</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -9677,15 +9689,19 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Kaelon</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr"/>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>kaelon@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D478" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9695,12 +9711,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>anderson</t>
+          <t>Burkitt</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -9713,12 +9729,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Suzy</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Gardner</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
@@ -9731,12 +9747,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Crossfit</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Pickleball</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
@@ -9749,19 +9765,15 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Van rooyen</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>tvanrooyan@rodger.com</t>
-        </is>
-      </c>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9771,12 +9783,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Jasper</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Varney</t>
+          <t>anderson</t>
         </is>
       </c>
       <c r="C483" t="inlineStr"/>
@@ -9789,12 +9801,12 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Suzy</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Tully</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
@@ -9807,12 +9819,12 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Caleb</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Pena</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -9825,15 +9837,19 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Arnie</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Pena</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr"/>
+          <t>Van rooyen</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>tvanrooyan@rodger.com</t>
+        </is>
+      </c>
       <c r="D486" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9843,12 +9859,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>linh</t>
+          <t>Jasper</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>Varney</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
@@ -9861,17 +9877,17 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Jacetine</t>
+          <t>antonio</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Wright</t>
+          <t>Coelho</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>jacetinebayno@gmail.com</t>
+          <t>tonycoelho83@gmail.com</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -9883,19 +9899,15 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>akemail11@icloud.com</t>
-        </is>
-      </c>
+          <t>Tully</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9905,19 +9917,15 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Lorie</t>
+          <t>Caleb</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Desjardins</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>managerdesjardins2015@gmail.com</t>
-        </is>
-      </c>
+          <t>Pena</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9927,19 +9935,15 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Arnie</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>lindarush99@gmail.com</t>
-        </is>
-      </c>
+          <t>Pena</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9949,19 +9953,15 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Chantelle</t>
+          <t>linh</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Lawrence</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>chantelle.l0812@gmail.com</t>
-        </is>
-      </c>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -9971,17 +9971,17 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Trieu</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>wendygibson0@gmail.com</t>
+          <t>trieu.susan@gmail.com</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -9993,19 +9993,15 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Ambrose</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>graham_lisa@hotmail.com</t>
-        </is>
-      </c>
+          <t>Cowen</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10015,17 +10011,17 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Treefrog</t>
+          <t>Jacetine</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>j.vogler@treefrog.ca</t>
+          <t>jacetinebayno@gmail.com</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -10037,17 +10033,17 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Tidi</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>stidi@herculesca.ca</t>
+          <t>akemail11@icloud.com</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -10059,17 +10055,17 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>Lorie</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Rey</t>
+          <t>Desjardins</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>rmrey1976@hotmail.com</t>
+          <t>managerdesjardins2015@gmail.com</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -10081,15 +10077,19 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Sutherland</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr"/>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>lindarush99@gmail.com</t>
+        </is>
+      </c>
       <c r="D498" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10099,15 +10099,19 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Deana</t>
+          <t>Chantelle</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Wannamaker</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr"/>
+          <t>Lawrence</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>chantelle.l0812@gmail.com</t>
+        </is>
+      </c>
       <c r="D499" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10117,17 +10121,17 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Legaspi</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>nicholas.legaspi@thecanadianbrewhouse.com</t>
+          <t>wendygibson0@gmail.com</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -10139,17 +10143,17 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Michele</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Bumbacco</t>
+          <t>Ambrose</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>michelebumbacco@gmail.com</t>
+          <t>graham_lisa@hotmail.com</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -10161,17 +10165,17 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Treefrog</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Sisu</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>sansisu888@gmail.com</t>
+          <t>j.vogler@treefrog.ca</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -10183,17 +10187,17 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Leslie</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Tidi</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>leslie.nguyen@bell.net</t>
+          <t>stidi@herculesca.ca</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -10205,15 +10209,19 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Esther</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr"/>
+          <t>Rey</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>rmrey1976@hotmail.com</t>
+        </is>
+      </c>
       <c r="D504" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10223,19 +10231,15 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Jasmyn</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Farquharson</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>southeastbarrie.admin@f45training.com</t>
-        </is>
-      </c>
+          <t>Sutherland</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10245,19 +10249,15 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Deana</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Burnett</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>tiffany.burnett@live.com</t>
-        </is>
-      </c>
+          <t>Wannamaker</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10267,15 +10267,19 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Campbell</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr"/>
+          <t>Legaspi</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>nicholas.legaspi@thecanadianbrewhouse.com</t>
+        </is>
+      </c>
       <c r="D507" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10285,15 +10289,19 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Michele</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Campbell</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr"/>
+          <t>Bumbacco</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>michelebumbacco@gmail.com</t>
+        </is>
+      </c>
       <c r="D508" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10303,17 +10311,17 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Arpa</t>
+          <t>Sisu</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>gillian.arpa@rogers.com</t>
+          <t>sansisu888@gmail.com</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -10325,15 +10333,19 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Vidya</t>
+          <t>Leslie</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Hariharan</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr"/>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>leslie.nguyen@bell.net</t>
+        </is>
+      </c>
       <c r="D510" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10343,12 +10355,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Krishav</t>
+          <t>Esther</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Prasad</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
@@ -10361,15 +10373,19 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Sarika</t>
+          <t>Jasmyn</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Sankar</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr"/>
+          <t>Farquharson</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>southeastbarrie.admin@f45training.com</t>
+        </is>
+      </c>
       <c r="D512" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10379,17 +10395,17 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>DOMINIQUE</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>NGUYEN</t>
+          <t>Burnett</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>dominiqueti@hotmail.com</t>
+          <t>tiffany.burnett@live.com</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -10401,12 +10417,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Colbeck</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="C514" t="inlineStr"/>
@@ -10419,19 +10435,15 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Waldie</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>jwaldie13@gmail.com</t>
-        </is>
-      </c>
+          <t>Campbell</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr"/>
       <c r="D515" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10441,15 +10453,19 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Jaden</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Greene</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr"/>
+          <t>Arpa</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>gillian.arpa@rogers.com</t>
+        </is>
+      </c>
       <c r="D516" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10459,12 +10475,12 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Vidya</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Young 2.0</t>
+          <t>Hariharan</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
@@ -10477,12 +10493,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Nathaniel</t>
+          <t>Krishav</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Greene</t>
+          <t>Prasad</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
@@ -10495,12 +10511,12 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Winston</t>
+          <t>Sarika</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Greene</t>
+          <t>Sankar</t>
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
@@ -10513,17 +10529,17 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Elham</t>
+          <t>DOMINIQUE</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Emami</t>
+          <t>NGUYEN</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>elham.emami42@gmail.com</t>
+          <t>dominiqueti@hotmail.com</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -10535,12 +10551,12 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Mandy M</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Colbeck</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -10553,15 +10569,19 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Tristan</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Correia</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr"/>
+          <t>Waldie</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>jwaldie13@gmail.com</t>
+        </is>
+      </c>
       <c r="D522" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10571,12 +10591,12 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Jaden</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>McConnachie</t>
+          <t>Greene</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -10589,12 +10609,12 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Stacy</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Tremain 2.0</t>
+          <t>Young 2.0</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -10607,12 +10627,12 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Kerrie</t>
+          <t>Nathaniel</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Lawson</t>
+          <t>Greene</t>
         </is>
       </c>
       <c r="C525" t="inlineStr"/>
@@ -10625,19 +10645,15 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>Winston</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Andrade</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>andradehome@rogers.com</t>
-        </is>
-      </c>
+          <t>Greene</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr"/>
       <c r="D526" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10647,17 +10663,17 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Elham</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Dunn</t>
+          <t>Emami</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>michelled@buschsystems.com</t>
+          <t>elham.emami42@gmail.com</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -10669,19 +10685,15 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Pauline</t>
+          <t>Mandy M</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Stevenson</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>pstevenson282727@gmail.com</t>
-        </is>
-      </c>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr"/>
       <c r="D528" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10691,19 +10703,15 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Dennis</t>
+          <t>Tristan</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Crossland</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>denniscrossland@hotmail.com</t>
-        </is>
-      </c>
+          <t>Correia</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10713,19 +10721,15 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Silva</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>ana@solutionswithimpact.com</t>
-        </is>
-      </c>
+          <t>McConnachie</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10735,19 +10739,15 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Stacy</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Soule</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>angela.soule@barrie.ca</t>
-        </is>
-      </c>
+          <t>Tremain 2.0</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10757,19 +10757,15 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Kerrie</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Teodoro</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>dteodoro73@gmail.com</t>
-        </is>
-      </c>
+          <t>Lawson</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10779,17 +10775,17 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Cooper</t>
+          <t>Joe</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Tomkinson</t>
+          <t>Andrade</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>ctomkinson@oatleyvigmond.com</t>
+          <t>andradehome@rogers.com</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -10801,17 +10797,17 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Griffith</t>
+          <t>Dunn</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>sgriffith@geiconsultants.com</t>
+          <t>michelled@buschsystems.com</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -10823,17 +10819,17 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>rowan</t>
+          <t>Pauline</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>edwards</t>
+          <t>Stevenson</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>rowanedwards25@gmail.com</t>
+          <t>pstevenson282727@gmail.com</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -10845,17 +10841,17 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Tanya</t>
+          <t>Dennis</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Smet</t>
+          <t>Crossland</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>tanya.smet@stratawealth.ca</t>
+          <t>denniscrossland@hotmail.com</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -10867,15 +10863,19 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Taylin</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Winacott</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr"/>
+          <t>Silva</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>ana@solutionswithimpact.com</t>
+        </is>
+      </c>
       <c r="D537" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
@@ -10885,16 +10885,516 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Soule</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>angela.soule@barrie.ca</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Danny</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Teodoro</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>dteodoro73@gmail.com</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Cooper</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Tomkinson</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>ctomkinson@oatleyvigmond.com</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Griffith</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>sgriffith@geiconsultants.com</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Rouzbeh</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>rouzbehhz@gmail.com</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>rowan</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>edwards</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>rowanedwards25@gmail.com</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Tanya</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Smet</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>tanya.smet@stratawealth.ca</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Taylin</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Winacott</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
           <t>Kaiden</t>
         </is>
       </c>
-      <c r="B538" t="inlineStr">
+      <c r="B546" t="inlineStr">
         <is>
           <t>Winacott</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr">
+      <c r="C546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Lawryshyn</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>lawryshync@gmail.com</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Franchino</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Franchino</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Harsh</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>hp10537@gmail.com</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Seney</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>chris@chrisseney.com</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Alicia</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Basaraba</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>adrianandalicia@rogers.com</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Joshua</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Begale</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Jagi</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>begalesingh21@gmail.com</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Basaraba</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Cindy</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Howarth</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>cindy@thegreystonegroup.ca</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Aaliya Singh</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>sangwan</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Savita</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Pahil</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Conforti</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>whittlewoodworks2023@gmail.com</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Tom</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Leggatt</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>bluesbrothers@rogers.com</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Lauren</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>O'Hara</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>laurohara91@gmail.com</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Elio</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Pinta</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>pintaelio7@gmail.com</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Barrie.xlsx
+++ b/docs/downloads/Barrie.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D562"/>
+  <dimension ref="A1:D565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2393,17 +2393,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Somya</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Paliwal</t>
+          <t>Mammoliti</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>somyapaliwal@hotmail.com</t>
+          <t>anna.mochizuki@rogers.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2415,17 +2415,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Carroll</t>
+          <t>Somya</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Balot</t>
+          <t>Paliwal</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>carroll.balot@utoronto.ca</t>
+          <t>somyapaliwal@hotmail.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2437,17 +2437,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Raelene</t>
+          <t>Carroll</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Gannon</t>
+          <t>Balot</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>raesources@gmail.com</t>
+          <t>carroll.balot@utoronto.ca</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2459,17 +2459,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Raelene</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Farrugia</t>
+          <t>Gannon</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>farrugia2020@yahoo.com</t>
+          <t>raesources@gmail.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2481,17 +2481,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Yunus</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Farrugia</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>yunusmohamed22@gmail.com</t>
+          <t>farrugia2020@yahoo.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2503,17 +2503,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Yunus</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>craig@aardvark.one</t>
+          <t>yunusmohamed22@gmail.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2525,17 +2525,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dick</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>sarah_carruthers00@hotmail.com</t>
+          <t>craig@aardvark.one</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2547,17 +2547,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lourenco</t>
+          <t>Dick</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>owenlourenco120@gmail.com</t>
+          <t>sarah_carruthers00@hotmail.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2569,17 +2569,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Deborah</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Howe</t>
+          <t>Lourenco</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>debbiehowe2000@yahoo.com</t>
+          <t>owenlourenco120@gmail.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2591,17 +2591,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Deborah</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Grube</t>
+          <t>Howe</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>grubee3@gmail.com</t>
+          <t>debbiehowe2000@yahoo.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2613,17 +2613,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ken</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Gilmer</t>
+          <t>Grube</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>kenneth.gilmer@garda.com</t>
+          <t>grubee3@gmail.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2635,17 +2635,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kaelon</t>
+          <t>Ken</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Clark</t>
+          <t>Gilmer</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>kaelonbuckle@outlook.com</t>
+          <t>kenneth.gilmer@garda.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2657,17 +2657,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Joanne</t>
+          <t>Kaelon</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Medeiros</t>
+          <t>Clark</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>j95@rogers.com</t>
+          <t>kaelonbuckle@outlook.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2679,17 +2679,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Joanne</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Amon</t>
+          <t>Medeiros</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>inch4now@gmail.com</t>
+          <t>j95@rogers.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2701,17 +2701,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Arbour</t>
+          <t>Amon</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ames86@live.ca</t>
+          <t>inch4now@gmail.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2723,17 +2723,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>Arbour</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>dcgconsulting@rogers.com</t>
+          <t>ames86@live.ca</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2745,17 +2745,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Holly</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lundrigan</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>hollster15@hotmail.com</t>
+          <t>dcgconsulting@rogers.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2767,17 +2767,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Holly</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Hamlin</t>
+          <t>Lundrigan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>khamlinccimusic@gmail.com</t>
+          <t>hollster15@hotmail.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2789,17 +2789,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Medeiros</t>
+          <t>Hamlin</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>david@david99.ca</t>
+          <t>khamlinccimusic@gmail.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2811,17 +2811,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Dennis</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Miropolsky</t>
+          <t>Medeiros</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>dennismirop@gmail.com</t>
+          <t>david@david99.ca</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Annemarie</t>
+          <t>Dennis</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Hill</t>
+          <t>Miropolsky</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>lsannemarieh@gmail.com</t>
+          <t>dennismirop@gmail.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2855,17 +2855,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Audree</t>
+          <t>Annemarie</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Andal</t>
+          <t>Hill</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>audree.andal@gmail.com</t>
+          <t>lsannemarieh@gmail.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2877,17 +2877,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Brenna</t>
+          <t>Audree</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Grinnell</t>
+          <t>Andal</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>bkh.mail01@gmail.com</t>
+          <t>audree.andal@gmail.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2899,17 +2899,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Janelle</t>
+          <t>Brenna</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Albert</t>
+          <t>Grinnell</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>janelle.albert@hotmail.com</t>
+          <t>bkh.mail01@gmail.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2921,17 +2921,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Janelle</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Albert</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>codygreen27@hotmail.com</t>
+          <t>janelle.albert@hotmail.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2943,17 +2943,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nayyar</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>samanthanayyar@gmail.ca</t>
+          <t>codygreen27@hotmail.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2965,17 +2965,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Stan</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Czachor</t>
+          <t>Nayyar</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>stanczachor@luxlightingservices.com</t>
+          <t>samanthanayyar@gmail.ca</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2987,17 +2987,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Stan</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cross</t>
+          <t>Czachor</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>mattcross17@hotmail.com</t>
+          <t>stanczachor@luxlightingservices.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3009,17 +3009,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Dannette</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Berard</t>
+          <t>Cross</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>carisse1777@gmail.com</t>
+          <t>mattcross17@hotmail.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3031,17 +3031,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Amrinder</t>
+          <t>Dannette</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Kang</t>
+          <t>Berard</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>280propertymanagement@gmail.com</t>
+          <t>carisse1777@gmail.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3053,17 +3053,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Colleen</t>
+          <t>Amrinder</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Crosby</t>
+          <t>Kang</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>cecrosbycct@gmail.com</t>
+          <t>280propertymanagement@gmail.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3075,17 +3075,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Colleen</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Blanchard</t>
+          <t>Crosby</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ggcc1717@gmail.com</t>
+          <t>cecrosbycct@gmail.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3097,17 +3097,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Kris</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Blanchard</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>kris_johnson11@hotmail.com</t>
+          <t>ggcc1717@gmail.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3119,17 +3119,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Jessie</t>
+          <t>Kris</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>yyjessiechan@gmail.com</t>
+          <t>kris_johnson11@hotmail.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3141,17 +3141,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Jessie</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cisneros</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>manuelcisnerosleyva@gmail.com</t>
+          <t>yyjessiechan@gmail.com</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3163,17 +3163,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Alicia</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>Cisneros</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>alicia.gauthier@gmail.com</t>
+          <t>manuelcisnerosleyva@gmail.com</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3185,17 +3185,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Doe</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>cbayford@webersupply.com</t>
+          <t>alicia.gauthier@gmail.com</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3207,17 +3207,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Desmond</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Payne</t>
+          <t>Doe</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>dezz.payne@gmail.com</t>
+          <t>cbayford@webersupply.com</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3229,17 +3229,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Desmond</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Beauchesne</t>
+          <t>Payne</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>lbeauchesne@smcdsb.on.ca</t>
+          <t>dezz.payne@gmail.com</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3251,17 +3251,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Kuznik</t>
+          <t>Beauchesne</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>peterfkuznik@gmail.com</t>
+          <t>lbeauchesne@smcdsb.on.ca</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3273,17 +3273,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Trudy</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Argue</t>
+          <t>Kuznik</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>trudy.argue@hotmail.com</t>
+          <t>peterfkuznik@gmail.com</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3295,17 +3295,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Trudy</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Argue</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>steph_carter@live.com</t>
+          <t>trudy.argue@hotmail.com</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3317,17 +3317,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Burns</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>michelleburnscoach@gmail.com</t>
+          <t>steph_carter@live.com</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3339,17 +3339,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Billy</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Burns</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>billy.miller01@gmail.com</t>
+          <t>michelleburnscoach@gmail.com</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3361,17 +3361,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Billy</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>christopheryoung7861@gmail.com</t>
+          <t>billy.miller01@gmail.com</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3383,17 +3383,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Beau</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>beauscott1@gmail.com</t>
+          <t>christopheryoung7861@gmail.com</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3405,17 +3405,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Beau</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>tedjarvis54@gmail.com</t>
+          <t>beauscott1@gmail.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3427,17 +3427,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mantas</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>mantas@rogers.com</t>
+          <t>tedjarvis54@gmail.com</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3449,17 +3449,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jo-ann</t>
+          <t>Nick</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Giorshev</t>
+          <t>Mantas</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>joanngiorshev@gmail.com</t>
+          <t>mantas@rogers.com</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3471,17 +3471,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Jo-ann</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Stpierre</t>
+          <t>Giorshev</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>stpierre_m@hotmail.com</t>
+          <t>joanngiorshev@gmail.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3493,17 +3493,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Devenyi</t>
+          <t>Stpierre</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>b.devenyi@me.com</t>
+          <t>stpierre_m@hotmail.com</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3515,17 +3515,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Rhonda</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Devenyi</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>rlbailet60@gmail.com</t>
+          <t>b.devenyi@me.com</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3537,17 +3537,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Jaskiran</t>
+          <t>Rhonda</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nijjar</t>
+          <t>Bailey</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>jaskiranamrinder@gmail.com</t>
+          <t>rlbailet60@gmail.com</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3559,17 +3559,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Colin</t>
+          <t>Jaskiran</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Mcfadyen</t>
+          <t>Nijjar</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>blackstonepba@outlook.com</t>
+          <t>jaskiranamrinder@gmail.com</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -11395,6 +11395,72 @@
         </is>
       </c>
       <c r="D562" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>GRAIG</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>FRASER</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>gmfraser1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Gabriele</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>gabeprimavera@gmail.com</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>barrie@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Ray</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>heather.ray15@gmail.com</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
         <is>
           <t>barrie@pickleplex.ca</t>
         </is>
